--- a/So_do_(tên_mốc_mua).xlsx
+++ b/So_do_(tên_mốc_mua).xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="49">
   <si>
     <t>SỔ ĐO THỦY CHUẨN HẠNG 4</t>
   </si>
@@ -540,7 +540,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N152"/>
+  <dimension ref="A1:N100"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -731,22 +731,22 @@
         <v>1</v>
       </c>
       <c r="C13" s="1">
-        <v>2259</v>
+        <v>2462</v>
       </c>
       <c r="E13" s="1">
-        <v>2266</v>
+        <v>2429</v>
       </c>
       <c r="F13" t="s">
         <v>43</v>
       </c>
       <c r="H13" s="1">
-        <v>1995</v>
+        <v>2012</v>
       </c>
       <c r="I13" s="1">
-        <v>6571</v>
+        <v>6586</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L13" t="s">
         <v>44</v>
@@ -757,22 +757,22 @@
     </row>
     <row r="14" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C14" s="1">
-        <v>1731</v>
+        <v>1562</v>
       </c>
       <c r="E14" s="1">
-        <v>1688</v>
+        <v>1479</v>
       </c>
       <c r="F14" t="s">
         <v>45</v>
       </c>
       <c r="H14" s="1">
-        <v>1977</v>
+        <v>1954</v>
       </c>
       <c r="I14" s="1">
-        <v>6451</v>
+        <v>6427</v>
       </c>
       <c r="J14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L14" t="s">
         <v>46</v>
@@ -783,25 +783,25 @@
     </row>
     <row r="15" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C15">
-        <v>52.8</v>
+        <v>90</v>
       </c>
       <c r="E15">
-        <v>57.8</v>
+        <v>95</v>
       </c>
       <c r="F15" t="s">
         <v>47</v>
       </c>
       <c r="H15">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="I15">
-        <v>120</v>
+        <v>159</v>
       </c>
       <c r="J15">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="K15">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="N15">
         <v>100</v>
@@ -820,22 +820,22 @@
         <v>2</v>
       </c>
       <c r="C17" s="1">
-        <v>2271</v>
+        <v>2390</v>
       </c>
       <c r="E17" s="1">
-        <v>2279</v>
+        <v>2440</v>
       </c>
       <c r="F17" t="s">
         <v>43</v>
       </c>
       <c r="H17" s="1">
-        <v>2007</v>
+        <v>1950</v>
       </c>
       <c r="I17" s="1">
-        <v>6484</v>
+        <v>6425</v>
       </c>
       <c r="J17">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L17" t="s">
         <v>46</v>
@@ -846,22 +846,22 @@
     </row>
     <row r="18" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C18" s="1">
-        <v>1743</v>
+        <v>1507</v>
       </c>
       <c r="E18" s="1">
-        <v>1711</v>
+        <v>1507</v>
       </c>
       <c r="F18" t="s">
         <v>45</v>
       </c>
       <c r="H18" s="1">
-        <v>1995</v>
+        <v>1975</v>
       </c>
       <c r="I18" s="1">
-        <v>6570</v>
+        <v>6548</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L18" t="s">
         <v>44</v>
@@ -872,25 +872,25 @@
     </row>
     <row r="19" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C19">
-        <v>52.8</v>
+        <v>88.3</v>
       </c>
       <c r="E19">
-        <v>56.8</v>
+        <v>93.3</v>
       </c>
       <c r="F19" t="s">
         <v>47</v>
       </c>
       <c r="H19">
-        <v>12</v>
+        <v>-25</v>
       </c>
       <c r="I19">
-        <v>-86</v>
+        <v>-123</v>
       </c>
       <c r="J19">
         <v>-2</v>
       </c>
       <c r="K19">
-        <v>14</v>
+        <v>-23</v>
       </c>
       <c r="N19">
         <v>100</v>
@@ -898,7 +898,7 @@
     </row>
     <row r="20" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C20">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="E20">
         <f>E16+C20</f>
@@ -909,22 +909,22 @@
         <v>3</v>
       </c>
       <c r="C21" s="1">
-        <v>2291</v>
+        <v>2426</v>
       </c>
       <c r="E21" s="1">
-        <v>2276</v>
+        <v>2409</v>
       </c>
       <c r="F21" t="s">
         <v>43</v>
       </c>
       <c r="H21" s="1">
-        <v>2027</v>
+        <v>2025</v>
       </c>
       <c r="I21" s="1">
-        <v>6602</v>
+        <v>6599</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="s">
         <v>44</v>
@@ -935,22 +935,22 @@
     </row>
     <row r="22" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C22" s="1">
-        <v>1763</v>
+        <v>1626</v>
       </c>
       <c r="E22" s="1">
-        <v>1750</v>
+        <v>1559</v>
       </c>
       <c r="F22" t="s">
         <v>45</v>
       </c>
       <c r="H22" s="1">
-        <v>2013</v>
+        <v>1982</v>
       </c>
       <c r="I22" s="1">
-        <v>6486</v>
+        <v>6458</v>
       </c>
       <c r="J22">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L22" t="s">
         <v>46</v>
@@ -961,25 +961,25 @@
     </row>
     <row r="23" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C23">
-        <v>52.8</v>
+        <v>80</v>
       </c>
       <c r="E23">
-        <v>52.6</v>
+        <v>85</v>
       </c>
       <c r="F23" t="s">
         <v>47</v>
       </c>
       <c r="H23">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="I23">
-        <v>116</v>
+        <v>141</v>
       </c>
       <c r="J23">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="K23">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="N23">
         <v>100</v>
@@ -987,7 +987,7 @@
     </row>
     <row r="24" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C24">
-        <v>0.2</v>
+        <v>-5</v>
       </c>
       <c r="E24">
         <f>E20+C24</f>
@@ -998,22 +998,22 @@
         <v>4</v>
       </c>
       <c r="C25" s="1">
-        <v>2303</v>
+        <v>2422</v>
       </c>
       <c r="E25" s="1">
-        <v>2286</v>
+        <v>2475</v>
       </c>
       <c r="F25" t="s">
         <v>43</v>
       </c>
       <c r="H25" s="1">
-        <v>2039</v>
+        <v>1973</v>
       </c>
       <c r="I25" s="1">
-        <v>6514</v>
+        <v>6449</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L25" t="s">
         <v>46</v>
@@ -1024,22 +1024,22 @@
     </row>
     <row r="26" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C26" s="1">
-        <v>1775</v>
+        <v>1522</v>
       </c>
       <c r="E26" s="1">
-        <v>1772</v>
+        <v>1525</v>
       </c>
       <c r="F26" t="s">
         <v>45</v>
       </c>
       <c r="H26" s="1">
-        <v>2029</v>
+        <v>2000</v>
       </c>
       <c r="I26" s="1">
-        <v>6602</v>
+        <v>6574</v>
       </c>
       <c r="J26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L26" t="s">
         <v>44</v>
@@ -1050,25 +1050,25 @@
     </row>
     <row r="27" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C27">
-        <v>52.8</v>
+        <v>90</v>
       </c>
       <c r="E27">
-        <v>51.4</v>
+        <v>95</v>
       </c>
       <c r="F27" t="s">
         <v>47</v>
       </c>
       <c r="H27">
-        <v>10</v>
+        <v>-27</v>
       </c>
       <c r="I27">
-        <v>-88</v>
+        <v>-125</v>
       </c>
       <c r="J27">
         <v>-2</v>
       </c>
       <c r="K27">
-        <v>12</v>
+        <v>-25</v>
       </c>
       <c r="N27">
         <v>100</v>
@@ -1076,7 +1076,7 @@
     </row>
     <row r="28" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C28">
-        <v>1.4</v>
+        <v>-5</v>
       </c>
       <c r="E28">
         <f>E24+C28</f>
@@ -1087,22 +1087,22 @@
         <v>5</v>
       </c>
       <c r="C29" s="1">
-        <v>2323</v>
+        <v>2503</v>
       </c>
       <c r="E29" s="1">
-        <v>2293</v>
+        <v>2497</v>
       </c>
       <c r="F29" t="s">
         <v>43</v>
       </c>
       <c r="H29" s="1">
-        <v>2059</v>
+        <v>2052</v>
       </c>
       <c r="I29" s="1">
-        <v>6635</v>
+        <v>6627</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L29" t="s">
         <v>44</v>
@@ -1113,22 +1113,22 @@
     </row>
     <row r="30" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C30" s="1">
-        <v>1795</v>
+        <v>1603</v>
       </c>
       <c r="E30" s="1">
-        <v>1790</v>
+        <v>1547</v>
       </c>
       <c r="F30" t="s">
         <v>45</v>
       </c>
       <c r="H30" s="1">
-        <v>2041</v>
+        <v>2022</v>
       </c>
       <c r="I30" s="1">
-        <v>6515</v>
+        <v>6499</v>
       </c>
       <c r="J30">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L30" t="s">
         <v>46</v>
@@ -1139,25 +1139,25 @@
     </row>
     <row r="31" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C31">
-        <v>52.8</v>
+        <v>90</v>
       </c>
       <c r="E31">
-        <v>50.3</v>
+        <v>95</v>
       </c>
       <c r="F31" t="s">
         <v>47</v>
       </c>
       <c r="H31">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="I31">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="J31">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="K31">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="N31">
         <v>100</v>
@@ -1165,7 +1165,7 @@
     </row>
     <row r="32" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C32">
-        <v>2.5</v>
+        <v>-5</v>
       </c>
       <c r="E32">
         <f>E28+C32</f>
@@ -1176,22 +1176,22 @@
         <v>6</v>
       </c>
       <c r="C33" s="1">
-        <v>2344</v>
+        <v>2532</v>
       </c>
       <c r="E33" s="1">
-        <v>2320</v>
+        <v>2480</v>
       </c>
       <c r="F33" t="s">
         <v>43</v>
       </c>
       <c r="H33" s="1">
-        <v>2080</v>
+        <v>2102</v>
       </c>
       <c r="I33" s="1">
-        <v>6556</v>
+        <v>6577</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L33" t="s">
         <v>46</v>
@@ -1202,22 +1202,22 @@
     </row>
     <row r="34" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C34" s="1">
-        <v>1816</v>
+        <v>1672</v>
       </c>
       <c r="E34" s="1">
-        <v>1811</v>
+        <v>1598</v>
       </c>
       <c r="F34" t="s">
         <v>45</v>
       </c>
       <c r="H34" s="1">
-        <v>2065</v>
+        <v>2040</v>
       </c>
       <c r="I34" s="1">
-        <v>6639</v>
+        <v>6613</v>
       </c>
       <c r="J34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L34" t="s">
         <v>44</v>
@@ -1228,25 +1228,25 @@
     </row>
     <row r="35" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C35">
-        <v>52.8</v>
+        <v>86</v>
       </c>
       <c r="E35">
-        <v>50.9</v>
+        <v>88.2</v>
       </c>
       <c r="F35" t="s">
         <v>47</v>
       </c>
       <c r="H35">
-        <v>15</v>
+        <v>62</v>
       </c>
       <c r="I35">
-        <v>-83</v>
+        <v>-36</v>
       </c>
       <c r="J35">
         <v>-2</v>
       </c>
       <c r="K35">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="N35">
         <v>100</v>
@@ -1254,7 +1254,7 @@
     </row>
     <row r="36" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C36">
-        <v>1.9</v>
+        <v>-2.2</v>
       </c>
       <c r="E36">
         <f>E32+C36</f>
@@ -1265,22 +1265,22 @@
         <v>7</v>
       </c>
       <c r="C37" s="1">
-        <v>2381</v>
+        <v>2487</v>
       </c>
       <c r="E37" s="1">
-        <v>2365</v>
+        <v>2497</v>
       </c>
       <c r="F37" t="s">
         <v>43</v>
       </c>
       <c r="H37" s="1">
-        <v>2117</v>
+        <v>2038</v>
       </c>
       <c r="I37" s="1">
-        <v>6692</v>
+        <v>6612</v>
       </c>
       <c r="J37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" t="s">
         <v>44</v>
@@ -1291,22 +1291,22 @@
     </row>
     <row r="38" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C38" s="1">
-        <v>1853</v>
+        <v>1587</v>
       </c>
       <c r="E38" s="1">
-        <v>1814</v>
+        <v>1597</v>
       </c>
       <c r="F38" t="s">
         <v>45</v>
       </c>
       <c r="H38" s="1">
-        <v>2089</v>
+        <v>2047</v>
       </c>
       <c r="I38" s="1">
-        <v>6562</v>
+        <v>6523</v>
       </c>
       <c r="J38">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L38" t="s">
         <v>46</v>
@@ -1317,25 +1317,25 @@
     </row>
     <row r="39" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C39">
-        <v>52.8</v>
+        <v>90</v>
       </c>
       <c r="E39">
-        <v>55.1</v>
+        <v>90</v>
       </c>
       <c r="F39" t="s">
         <v>47</v>
       </c>
       <c r="H39">
-        <v>28</v>
+        <v>-9</v>
       </c>
       <c r="I39">
-        <v>130</v>
+        <v>89</v>
       </c>
       <c r="J39">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="K39">
-        <v>30</v>
+        <v>-11</v>
       </c>
       <c r="N39">
         <v>100</v>
@@ -1343,7 +1343,7 @@
     </row>
     <row r="40" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C40">
-        <v>-2.3</v>
+        <v>0</v>
       </c>
       <c r="E40">
         <f>E36+C40</f>
@@ -1354,22 +1354,22 @@
         <v>8</v>
       </c>
       <c r="C41" s="1">
-        <v>2383</v>
+        <v>2493</v>
       </c>
       <c r="E41" s="1">
-        <v>2345</v>
+        <v>2444</v>
       </c>
       <c r="F41" t="s">
         <v>43</v>
       </c>
       <c r="H41" s="1">
-        <v>2119</v>
+        <v>2095</v>
       </c>
       <c r="I41" s="1">
-        <v>6595</v>
+        <v>6572</v>
       </c>
       <c r="J41">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="L41" t="s">
         <v>46</v>
@@ -1380,22 +1380,22 @@
     </row>
     <row r="42" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C42" s="1">
-        <v>1855</v>
+        <v>1693</v>
       </c>
       <c r="E42" s="1">
-        <v>1850</v>
+        <v>1675</v>
       </c>
       <c r="F42" t="s">
         <v>45</v>
       </c>
       <c r="H42" s="1">
-        <v>2097</v>
+        <v>2061</v>
       </c>
       <c r="I42" s="1">
-        <v>6671</v>
+        <v>6636</v>
       </c>
       <c r="J42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L42" t="s">
         <v>44</v>
@@ -1406,25 +1406,25 @@
     </row>
     <row r="43" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C43">
-        <v>52.8</v>
+        <v>80</v>
       </c>
       <c r="E43">
-        <v>49.5</v>
+        <v>76.9</v>
       </c>
       <c r="F43" t="s">
         <v>47</v>
       </c>
       <c r="H43">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="I43">
-        <v>-76</v>
+        <v>-64</v>
       </c>
       <c r="J43">
         <v>-2</v>
       </c>
       <c r="K43">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="N43">
         <v>100</v>
@@ -1432,7 +1432,7 @@
     </row>
     <row r="44" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C44">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="E44">
         <f>E40+C44</f>
@@ -1443,22 +1443,22 @@
         <v>9</v>
       </c>
       <c r="C45" s="1">
-        <v>2387</v>
+        <v>2511</v>
       </c>
       <c r="E45" s="1">
-        <v>2365</v>
+        <v>2466</v>
       </c>
       <c r="F45" t="s">
         <v>43</v>
       </c>
       <c r="H45" s="1">
-        <v>2123</v>
+        <v>2112</v>
       </c>
       <c r="I45" s="1">
-        <v>6700</v>
+        <v>6687</v>
       </c>
       <c r="J45">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L45" t="s">
         <v>44</v>
@@ -1469,22 +1469,22 @@
     </row>
     <row r="46" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C46" s="1">
-        <v>1859</v>
+        <v>1711</v>
       </c>
       <c r="E46" s="1">
-        <v>1865</v>
+        <v>1671</v>
       </c>
       <c r="F46" t="s">
         <v>45</v>
       </c>
       <c r="H46" s="1">
-        <v>2115</v>
+        <v>2069</v>
       </c>
       <c r="I46" s="1">
-        <v>6590</v>
+        <v>6546</v>
       </c>
       <c r="J46">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L46" t="s">
         <v>46</v>
@@ -1495,25 +1495,25 @@
     </row>
     <row r="47" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C47">
-        <v>52.8</v>
+        <v>80</v>
       </c>
       <c r="E47">
-        <v>50</v>
+        <v>79.5</v>
       </c>
       <c r="F47" t="s">
         <v>47</v>
       </c>
       <c r="H47">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="I47">
-        <v>110</v>
+        <v>141</v>
       </c>
       <c r="J47">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="K47">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="N47">
         <v>100</v>
@@ -1521,7 +1521,7 @@
     </row>
     <row r="48" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C48">
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="E48">
         <f>E44+C48</f>
@@ -1532,19 +1532,19 @@
         <v>10</v>
       </c>
       <c r="C49" s="1">
-        <v>2409</v>
+        <v>2595</v>
       </c>
       <c r="E49" s="1">
-        <v>2413</v>
+        <v>2527</v>
       </c>
       <c r="F49" t="s">
         <v>43</v>
       </c>
       <c r="H49" s="1">
-        <v>2145</v>
+        <v>2143</v>
       </c>
       <c r="I49" s="1">
-        <v>6620</v>
+        <v>6618</v>
       </c>
       <c r="J49">
         <v>0</v>
@@ -1558,19 +1558,19 @@
     </row>
     <row r="50" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C50" s="1">
-        <v>1881</v>
+        <v>1695</v>
       </c>
       <c r="E50" s="1">
-        <v>1863</v>
+        <v>1658</v>
       </c>
       <c r="F50" t="s">
         <v>45</v>
       </c>
       <c r="H50" s="1">
-        <v>2138</v>
+        <v>2092</v>
       </c>
       <c r="I50" s="1">
-        <v>6711</v>
+        <v>6665</v>
       </c>
       <c r="J50">
         <v>2</v>
@@ -1584,25 +1584,25 @@
     </row>
     <row r="51" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C51">
-        <v>52.8</v>
+        <v>90</v>
       </c>
       <c r="E51">
-        <v>55</v>
+        <v>86.9</v>
       </c>
       <c r="F51" t="s">
         <v>47</v>
       </c>
       <c r="H51">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="I51">
-        <v>-91</v>
+        <v>-47</v>
       </c>
       <c r="J51">
         <v>-2</v>
       </c>
       <c r="K51">
-        <v>9</v>
+        <v>53</v>
       </c>
       <c r="N51">
         <v>100</v>
@@ -1610,7 +1610,7 @@
     </row>
     <row r="52" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C52">
-        <v>-2.2</v>
+        <v>3.1</v>
       </c>
       <c r="E52">
         <f>E48+C52</f>
@@ -1621,22 +1621,22 @@
         <v>11</v>
       </c>
       <c r="C53" s="1">
-        <v>2443</v>
+        <v>2519</v>
       </c>
       <c r="E53" s="1">
-        <v>2432</v>
+        <v>2492</v>
       </c>
       <c r="F53" t="s">
         <v>43</v>
       </c>
       <c r="H53" s="1">
-        <v>2179</v>
+        <v>2118</v>
       </c>
       <c r="I53" s="1">
-        <v>6755</v>
+        <v>6691</v>
       </c>
       <c r="J53">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="L53" t="s">
         <v>44</v>
@@ -1647,22 +1647,22 @@
     </row>
     <row r="54" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C54" s="1">
-        <v>1915</v>
+        <v>1719</v>
       </c>
       <c r="E54" s="1">
-        <v>1878</v>
+        <v>1712</v>
       </c>
       <c r="F54" t="s">
         <v>45</v>
       </c>
       <c r="H54" s="1">
-        <v>2155</v>
+        <v>2101</v>
       </c>
       <c r="I54" s="1">
-        <v>6629</v>
+        <v>6576</v>
       </c>
       <c r="J54">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L54" t="s">
         <v>46</v>
@@ -1673,25 +1673,25 @@
     </row>
     <row r="55" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C55">
-        <v>52.8</v>
+        <v>80</v>
       </c>
       <c r="E55">
-        <v>55.4</v>
+        <v>78</v>
       </c>
       <c r="F55" t="s">
         <v>47</v>
       </c>
       <c r="H55">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="I55">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="J55">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="K55">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="N55">
         <v>100</v>
@@ -1699,7 +1699,7 @@
     </row>
     <row r="56" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C56">
-        <v>-2.6</v>
+        <v>2</v>
       </c>
       <c r="E56">
         <f>E52+C56</f>
@@ -1710,22 +1710,22 @@
         <v>12</v>
       </c>
       <c r="C57" s="1">
-        <v>2437</v>
+        <v>2561</v>
       </c>
       <c r="E57" s="1">
-        <v>2419</v>
+        <v>2517</v>
       </c>
       <c r="F57" t="s">
         <v>43</v>
       </c>
       <c r="H57" s="1">
-        <v>2173</v>
+        <v>2162</v>
       </c>
       <c r="I57" s="1">
-        <v>6648</v>
+        <v>6639</v>
       </c>
       <c r="J57">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L57" t="s">
         <v>46</v>
@@ -1736,22 +1736,22 @@
     </row>
     <row r="58" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C58" s="1">
-        <v>1909</v>
+        <v>1761</v>
       </c>
       <c r="E58" s="1">
-        <v>1910</v>
+        <v>1727</v>
       </c>
       <c r="F58" t="s">
         <v>45</v>
       </c>
       <c r="H58" s="1">
-        <v>2164</v>
+        <v>2123</v>
       </c>
       <c r="I58" s="1">
-        <v>6737</v>
+        <v>6698</v>
       </c>
       <c r="J58">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L58" t="s">
         <v>44</v>
@@ -1762,25 +1762,25 @@
     </row>
     <row r="59" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C59">
-        <v>52.8</v>
+        <v>80</v>
       </c>
       <c r="E59">
-        <v>50.9</v>
+        <v>79</v>
       </c>
       <c r="F59" t="s">
         <v>47</v>
       </c>
       <c r="H59">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="I59">
-        <v>-89</v>
+        <v>-59</v>
       </c>
       <c r="J59">
         <v>-2</v>
       </c>
       <c r="K59">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="N59">
         <v>100</v>
@@ -1788,7 +1788,7 @@
     </row>
     <row r="60" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C60">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="E60">
         <f>E56+C60</f>
@@ -1799,22 +1799,22 @@
         <v>13</v>
       </c>
       <c r="C61" s="1">
-        <v>2457</v>
+        <v>2582</v>
       </c>
       <c r="E61" s="1">
-        <v>2454</v>
+        <v>2599</v>
       </c>
       <c r="F61" t="s">
         <v>43</v>
       </c>
       <c r="H61" s="1">
-        <v>2193</v>
+        <v>2132</v>
       </c>
       <c r="I61" s="1">
-        <v>6768</v>
+        <v>6705</v>
       </c>
       <c r="J61">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L61" t="s">
         <v>44</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="62" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C62" s="1">
-        <v>1929</v>
+        <v>1682</v>
       </c>
       <c r="E62" s="1">
-        <v>1907</v>
+        <v>1685</v>
       </c>
       <c r="F62" t="s">
         <v>45</v>
       </c>
       <c r="H62" s="1">
-        <v>2180</v>
+        <v>2141</v>
       </c>
       <c r="I62" s="1">
-        <v>6653</v>
+        <v>6616</v>
       </c>
       <c r="J62">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L62" t="s">
         <v>46</v>
@@ -1851,25 +1851,25 @@
     </row>
     <row r="63" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C63">
-        <v>52.8</v>
+        <v>90</v>
       </c>
       <c r="E63">
-        <v>54.7</v>
+        <v>91.4</v>
       </c>
       <c r="F63" t="s">
         <v>47</v>
       </c>
       <c r="H63">
-        <v>13</v>
+        <v>-9</v>
       </c>
       <c r="I63">
-        <v>115</v>
+        <v>89</v>
       </c>
       <c r="J63">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="K63">
-        <v>15</v>
+        <v>-11</v>
       </c>
       <c r="N63">
         <v>100</v>
@@ -1877,7 +1877,7 @@
     </row>
     <row r="64" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C64">
-        <v>-1.9</v>
+        <v>-1.4</v>
       </c>
       <c r="E64">
         <f>E60+C64</f>
@@ -1888,22 +1888,22 @@
         <v>14</v>
       </c>
       <c r="C65" s="1">
-        <v>2468</v>
+        <v>2632</v>
       </c>
       <c r="E65" s="1">
-        <v>2450</v>
+        <v>2597</v>
       </c>
       <c r="F65" t="s">
         <v>43</v>
       </c>
       <c r="H65" s="1">
-        <v>2204</v>
+        <v>2182</v>
       </c>
       <c r="I65" s="1">
-        <v>6679</v>
+        <v>6659</v>
       </c>
       <c r="J65">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L65" t="s">
         <v>46</v>
@@ -1914,22 +1914,22 @@
     </row>
     <row r="66" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C66" s="1">
-        <v>1940</v>
+        <v>1732</v>
       </c>
       <c r="E66" s="1">
-        <v>1928</v>
+        <v>1703</v>
       </c>
       <c r="F66" t="s">
         <v>45</v>
       </c>
       <c r="H66" s="1">
-        <v>2189</v>
+        <v>2150</v>
       </c>
       <c r="I66" s="1">
-        <v>6762</v>
+        <v>6725</v>
       </c>
       <c r="J66">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L66" t="s">
         <v>44</v>
@@ -1940,25 +1940,25 @@
     </row>
     <row r="67" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C67">
-        <v>52.8</v>
+        <v>90</v>
       </c>
       <c r="E67">
-        <v>52.2</v>
+        <v>89.4</v>
       </c>
       <c r="F67" t="s">
         <v>47</v>
       </c>
       <c r="H67">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="I67">
-        <v>-83</v>
+        <v>-66</v>
       </c>
       <c r="J67">
         <v>-2</v>
       </c>
       <c r="K67">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="N67">
         <v>100</v>
@@ -1977,22 +1977,22 @@
         <v>15</v>
       </c>
       <c r="C69" s="1">
-        <v>2471</v>
+        <v>2636</v>
       </c>
       <c r="E69" s="1">
-        <v>2484</v>
+        <v>2572</v>
       </c>
       <c r="F69" t="s">
         <v>43</v>
       </c>
       <c r="H69" s="1">
-        <v>2207</v>
+        <v>2238</v>
       </c>
       <c r="I69" s="1">
-        <v>6784</v>
+        <v>6812</v>
       </c>
       <c r="J69">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="L69" t="s">
         <v>44</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="70" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C70" s="1">
-        <v>1943</v>
+        <v>1836</v>
       </c>
       <c r="E70" s="1">
-        <v>1913</v>
+        <v>1765</v>
       </c>
       <c r="F70" t="s">
         <v>45</v>
       </c>
       <c r="H70" s="1">
-        <v>2198</v>
+        <v>2171</v>
       </c>
       <c r="I70" s="1">
-        <v>6673</v>
+        <v>6647</v>
       </c>
       <c r="J70">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L70" t="s">
         <v>46</v>
@@ -2029,25 +2029,25 @@
     </row>
     <row r="71" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C71">
-        <v>52.8</v>
+        <v>80</v>
       </c>
       <c r="E71">
-        <v>57.1</v>
+        <v>80.7</v>
       </c>
       <c r="F71" t="s">
         <v>47</v>
       </c>
       <c r="H71">
-        <v>9</v>
+        <v>67</v>
       </c>
       <c r="I71">
-        <v>111</v>
+        <v>165</v>
       </c>
       <c r="J71">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="K71">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="N71">
         <v>100</v>
@@ -2055,7 +2055,7 @@
     </row>
     <row r="72" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C72">
-        <v>-4.3</v>
+        <v>-0.7</v>
       </c>
       <c r="E72">
         <f>E68+C72</f>
@@ -2066,22 +2066,22 @@
         <v>16</v>
       </c>
       <c r="C73" s="1">
-        <v>2494</v>
+        <v>2625</v>
       </c>
       <c r="E73" s="1">
-        <v>2471</v>
+        <v>2632</v>
       </c>
       <c r="F73" t="s">
         <v>43</v>
       </c>
       <c r="H73" s="1">
-        <v>2230</v>
+        <v>2176</v>
       </c>
       <c r="I73" s="1">
-        <v>6707</v>
+        <v>6651</v>
       </c>
       <c r="J73">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L73" t="s">
         <v>46</v>
@@ -2092,22 +2092,22 @@
     </row>
     <row r="74" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C74" s="1">
-        <v>1966</v>
+        <v>1725</v>
       </c>
       <c r="E74" s="1">
-        <v>1968</v>
+        <v>1739</v>
       </c>
       <c r="F74" t="s">
         <v>45</v>
       </c>
       <c r="H74" s="1">
-        <v>2219</v>
+        <v>2187</v>
       </c>
       <c r="I74" s="1">
-        <v>6794</v>
+        <v>6760</v>
       </c>
       <c r="J74">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L74" t="s">
         <v>44</v>
@@ -2118,25 +2118,25 @@
     </row>
     <row r="75" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C75">
-        <v>52.8</v>
+        <v>90</v>
       </c>
       <c r="E75">
-        <v>50.3</v>
+        <v>89.3</v>
       </c>
       <c r="F75" t="s">
         <v>47</v>
       </c>
       <c r="H75">
-        <v>11</v>
+        <v>-11</v>
       </c>
       <c r="I75">
-        <v>-87</v>
+        <v>-109</v>
       </c>
       <c r="J75">
         <v>-2</v>
       </c>
       <c r="K75">
-        <v>13</v>
+        <v>-9</v>
       </c>
       <c r="N75">
         <v>100</v>
@@ -2144,7 +2144,7 @@
     </row>
     <row r="76" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C76">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="E76">
         <f>E72+C76</f>
@@ -2155,22 +2155,22 @@
         <v>17</v>
       </c>
       <c r="C77" s="1">
-        <v>2511</v>
+        <v>2640</v>
       </c>
       <c r="E77" s="1">
-        <v>2502</v>
+        <v>2597</v>
       </c>
       <c r="F77" t="s">
         <v>43</v>
       </c>
       <c r="H77" s="1">
-        <v>2247</v>
+        <v>2237</v>
       </c>
       <c r="I77" s="1">
-        <v>6822</v>
+        <v>6811</v>
       </c>
       <c r="J77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L77" t="s">
         <v>44</v>
@@ -2181,22 +2181,22 @@
     </row>
     <row r="78" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C78" s="1">
-        <v>1983</v>
+        <v>1834</v>
       </c>
       <c r="E78" s="1">
-        <v>1952</v>
+        <v>1804</v>
       </c>
       <c r="F78" t="s">
         <v>45</v>
       </c>
       <c r="H78" s="1">
-        <v>2227</v>
+        <v>2200</v>
       </c>
       <c r="I78" s="1">
-        <v>6700</v>
+        <v>6676</v>
       </c>
       <c r="J78">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L78" t="s">
         <v>46</v>
@@ -2207,25 +2207,25 @@
     </row>
     <row r="79" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C79">
-        <v>52.8</v>
+        <v>80.6</v>
       </c>
       <c r="E79">
-        <v>55</v>
+        <v>79.3</v>
       </c>
       <c r="F79" t="s">
         <v>47</v>
       </c>
       <c r="H79">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="I79">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="J79">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="K79">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="N79">
         <v>100</v>
@@ -2233,7 +2233,7 @@
     </row>
     <row r="80" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C80">
-        <v>-2.2</v>
+        <v>1.3</v>
       </c>
       <c r="E80">
         <f>E76+C80</f>
@@ -2244,22 +2244,22 @@
         <v>18</v>
       </c>
       <c r="C81" s="1">
-        <v>2520</v>
+        <v>2653</v>
       </c>
       <c r="E81" s="1">
-        <v>2487</v>
+        <v>2645</v>
       </c>
       <c r="F81" t="s">
         <v>43</v>
       </c>
       <c r="H81" s="1">
-        <v>2256</v>
+        <v>2205</v>
       </c>
       <c r="I81" s="1">
-        <v>6733</v>
+        <v>6681</v>
       </c>
       <c r="J81">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L81" t="s">
         <v>46</v>
@@ -2270,22 +2270,22 @@
     </row>
     <row r="82" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C82" s="1">
-        <v>1992</v>
+        <v>1753</v>
       </c>
       <c r="E82" s="1">
-        <v>1993</v>
+        <v>1773</v>
       </c>
       <c r="F82" t="s">
         <v>45</v>
       </c>
       <c r="H82" s="1">
-        <v>2240</v>
+        <v>2210</v>
       </c>
       <c r="I82" s="1">
-        <v>6815</v>
+        <v>6784</v>
       </c>
       <c r="J82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L82" t="s">
         <v>44</v>
@@ -2296,25 +2296,25 @@
     </row>
     <row r="83" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C83">
-        <v>52.8</v>
+        <v>90</v>
       </c>
       <c r="E83">
-        <v>49.4</v>
+        <v>87.2</v>
       </c>
       <c r="F83" t="s">
         <v>47</v>
       </c>
       <c r="H83">
-        <v>16</v>
+        <v>-5</v>
       </c>
       <c r="I83">
-        <v>-82</v>
+        <v>-103</v>
       </c>
       <c r="J83">
         <v>-2</v>
       </c>
       <c r="K83">
-        <v>18</v>
+        <v>-3</v>
       </c>
       <c r="N83">
         <v>100</v>
@@ -2322,7 +2322,7 @@
     </row>
     <row r="84" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C84">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="E84">
         <f>E80+C84</f>
@@ -2333,22 +2333,22 @@
         <v>19</v>
       </c>
       <c r="C85" s="1">
-        <v>2541</v>
+        <v>2680</v>
       </c>
       <c r="E85" s="1">
-        <v>2508</v>
+        <v>2607</v>
       </c>
       <c r="F85" t="s">
         <v>43</v>
       </c>
       <c r="H85" s="1">
-        <v>2277</v>
+        <v>2282</v>
       </c>
       <c r="I85" s="1">
-        <v>6853</v>
+        <v>6857</v>
       </c>
       <c r="J85">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L85" t="s">
         <v>44</v>
@@ -2359,22 +2359,22 @@
     </row>
     <row r="86" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C86" s="1">
-        <v>2013</v>
+        <v>1880</v>
       </c>
       <c r="E86" s="1">
-        <v>1991</v>
+        <v>1847</v>
       </c>
       <c r="F86" t="s">
         <v>45</v>
       </c>
       <c r="H86" s="1">
-        <v>2249</v>
+        <v>2230</v>
       </c>
       <c r="I86" s="1">
-        <v>6723</v>
+        <v>6707</v>
       </c>
       <c r="J86">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L86" t="s">
         <v>46</v>
@@ -2385,25 +2385,25 @@
     </row>
     <row r="87" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C87">
-        <v>52.8</v>
+        <v>80</v>
       </c>
       <c r="E87">
-        <v>51.7</v>
+        <v>76</v>
       </c>
       <c r="F87" t="s">
         <v>47</v>
       </c>
       <c r="H87">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="I87">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="J87">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="K87">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="N87">
         <v>100</v>
@@ -2411,7 +2411,7 @@
     </row>
     <row r="88" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C88">
-        <v>1.1</v>
+        <v>4</v>
       </c>
       <c r="E88">
         <f>E84+C88</f>
@@ -2422,22 +2422,22 @@
         <v>20</v>
       </c>
       <c r="C89" s="1">
-        <v>2552</v>
+        <v>2717</v>
       </c>
       <c r="E89" s="1">
-        <v>2522</v>
+        <v>2669</v>
       </c>
       <c r="F89" t="s">
         <v>43</v>
       </c>
       <c r="H89" s="1">
-        <v>2288</v>
+        <v>2265</v>
       </c>
       <c r="I89" s="1">
-        <v>6765</v>
+        <v>6741</v>
       </c>
       <c r="J89">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L89" t="s">
         <v>46</v>
@@ -2448,22 +2448,22 @@
     </row>
     <row r="90" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C90" s="1">
-        <v>2024</v>
+        <v>1817</v>
       </c>
       <c r="E90" s="1">
-        <v>1999</v>
+        <v>1812</v>
       </c>
       <c r="F90" t="s">
         <v>45</v>
       </c>
       <c r="H90" s="1">
-        <v>2260</v>
+        <v>2240</v>
       </c>
       <c r="I90" s="1">
-        <v>6835</v>
+        <v>6814</v>
       </c>
       <c r="J90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L90" t="s">
         <v>44</v>
@@ -2474,25 +2474,25 @@
     </row>
     <row r="91" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C91">
-        <v>52.8</v>
+        <v>90</v>
       </c>
       <c r="E91">
-        <v>52.3</v>
+        <v>85.7</v>
       </c>
       <c r="F91" t="s">
         <v>47</v>
       </c>
       <c r="H91">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="I91">
-        <v>-70</v>
+        <v>-73</v>
       </c>
       <c r="J91">
         <v>-2</v>
       </c>
       <c r="K91">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="N91">
         <v>100</v>
@@ -2500,7 +2500,7 @@
     </row>
     <row r="92" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C92">
-        <v>0.5</v>
+        <v>4.3</v>
       </c>
       <c r="E92">
         <f>E88+C92</f>
@@ -2511,19 +2511,19 @@
         <v>21</v>
       </c>
       <c r="C93" s="1">
-        <v>2547</v>
+        <v>2694</v>
       </c>
       <c r="E93" s="1">
-        <v>2553</v>
+        <v>2652</v>
       </c>
       <c r="F93" t="s">
         <v>43</v>
       </c>
       <c r="H93" s="1">
-        <v>2283</v>
+        <v>2296</v>
       </c>
       <c r="I93" s="1">
-        <v>6858</v>
+        <v>6871</v>
       </c>
       <c r="J93">
         <v>0</v>
@@ -2537,22 +2537,22 @@
     </row>
     <row r="94" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C94" s="1">
-        <v>2019</v>
+        <v>1894</v>
       </c>
       <c r="E94" s="1">
-        <v>1999</v>
+        <v>1879</v>
       </c>
       <c r="F94" t="s">
         <v>45</v>
       </c>
       <c r="H94" s="1">
-        <v>2276</v>
+        <v>2263</v>
       </c>
       <c r="I94" s="1">
-        <v>6749</v>
+        <v>6740</v>
       </c>
       <c r="J94">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L94" t="s">
         <v>46</v>
@@ -2563,25 +2563,25 @@
     </row>
     <row r="95" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C95">
-        <v>52.8</v>
+        <v>80</v>
       </c>
       <c r="E95">
-        <v>55.4</v>
+        <v>77.3</v>
       </c>
       <c r="F95" t="s">
         <v>47</v>
       </c>
       <c r="H95">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="I95">
-        <v>109</v>
+        <v>131</v>
       </c>
       <c r="J95">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="K95">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="N95">
         <v>100</v>
@@ -2589,1240 +2589,83 @@
     </row>
     <row r="96" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C96">
-        <v>-2.6</v>
+        <v>2.7</v>
       </c>
       <c r="E96">
         <f>E92+C96</f>
       </c>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A97">
-        <v>22</v>
-      </c>
-      <c r="C97" s="1">
-        <v>2576</v>
-      </c>
-      <c r="E97" s="1">
-        <v>2554</v>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>48</v>
+      </c>
+      <c r="C97">
+        <v>53760</v>
+      </c>
+      <c r="E97">
+        <v>53243</v>
       </c>
       <c r="F97" t="s">
         <v>43</v>
       </c>
-      <c r="H97" s="1">
-        <v>2312</v>
-      </c>
-      <c r="I97" s="1">
-        <v>6789</v>
+      <c r="H97">
+        <v>44795</v>
+      </c>
+      <c r="I97">
+        <v>139870</v>
       </c>
       <c r="J97">
-        <v>-2</v>
-      </c>
-      <c r="L97" t="s">
-        <v>46</v>
-      </c>
-      <c r="N97">
-        <v>4575</v>
-      </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C98" s="1">
-        <v>2048</v>
-      </c>
-      <c r="E98" s="1">
-        <v>2049</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C98">
+        <v>35811</v>
+      </c>
+      <c r="E98">
+        <v>35262</v>
       </c>
       <c r="F98" t="s">
         <v>45</v>
       </c>
-      <c r="H98" s="1">
-        <v>2301</v>
-      </c>
-      <c r="I98" s="1">
-        <v>6876</v>
+      <c r="H98">
+        <v>44258</v>
+      </c>
+      <c r="I98">
+        <v>139232</v>
       </c>
       <c r="J98">
-        <v>0</v>
-      </c>
-      <c r="L98" t="s">
-        <v>44</v>
-      </c>
-      <c r="N98">
-        <v>4475</v>
-      </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C99">
-        <v>52.8</v>
+        <v>1794.9</v>
       </c>
       <c r="E99">
-        <v>50.5</v>
+        <v>1798.1</v>
       </c>
       <c r="F99" t="s">
         <v>47</v>
       </c>
       <c r="H99">
-        <v>11</v>
+        <v>537</v>
       </c>
       <c r="I99">
-        <v>-87</v>
+        <v>638</v>
       </c>
       <c r="J99">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="K99">
-        <v>13</v>
-      </c>
-      <c r="N99">
-        <v>100</v>
+        <v>537</v>
       </c>
     </row>
     <row r="100" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C100">
-        <v>2.3</v>
+        <v>-3.199999999999818</v>
       </c>
       <c r="E100">
-        <f>E96+C100</f>
-      </c>
-    </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A101">
-        <v>23</v>
-      </c>
-      <c r="C101" s="1">
-        <v>2604</v>
-      </c>
-      <c r="E101" s="1">
-        <v>2596</v>
-      </c>
-      <c r="F101" t="s">
-        <v>43</v>
-      </c>
-      <c r="H101" s="1">
-        <v>2340</v>
-      </c>
-      <c r="I101" s="1">
-        <v>6916</v>
-      </c>
-      <c r="J101">
-        <v>-1</v>
-      </c>
-      <c r="L101" t="s">
-        <v>44</v>
-      </c>
-      <c r="N101">
-        <v>4575</v>
-      </c>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C102" s="1">
-        <v>2076</v>
-      </c>
-      <c r="E102" s="1">
-        <v>2033</v>
-      </c>
-      <c r="F102" t="s">
-        <v>45</v>
-      </c>
-      <c r="H102" s="1">
-        <v>2314</v>
-      </c>
-      <c r="I102" s="1">
-        <v>6788</v>
-      </c>
-      <c r="J102">
-        <v>1</v>
-      </c>
-      <c r="L102" t="s">
-        <v>46</v>
-      </c>
-      <c r="N102">
-        <v>4475</v>
-      </c>
-    </row>
-    <row r="103" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C103">
-        <v>52.8</v>
-      </c>
-      <c r="E103">
-        <v>56.3</v>
-      </c>
-      <c r="F103" t="s">
-        <v>47</v>
-      </c>
-      <c r="H103">
-        <v>26</v>
-      </c>
-      <c r="I103">
-        <v>128</v>
-      </c>
-      <c r="J103">
-        <v>-2</v>
-      </c>
-      <c r="K103">
-        <v>28</v>
-      </c>
-      <c r="N103">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="104" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C104">
-        <v>-3.5</v>
-      </c>
-      <c r="E104">
-        <f>E100+C104</f>
-      </c>
-    </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A105">
-        <v>24</v>
-      </c>
-      <c r="C105" s="1">
-        <v>2610</v>
-      </c>
-      <c r="E105" s="1">
-        <v>2601</v>
-      </c>
-      <c r="F105" t="s">
-        <v>43</v>
-      </c>
-      <c r="H105" s="1">
-        <v>2346</v>
-      </c>
-      <c r="I105" s="1">
-        <v>6823</v>
-      </c>
-      <c r="J105">
-        <v>-2</v>
-      </c>
-      <c r="L105" t="s">
-        <v>46</v>
-      </c>
-      <c r="N105">
-        <v>4575</v>
-      </c>
-    </row>
-    <row r="106" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C106" s="1">
-        <v>2082</v>
-      </c>
-      <c r="E106" s="1">
-        <v>2075</v>
-      </c>
-      <c r="F106" t="s">
-        <v>45</v>
-      </c>
-      <c r="H106" s="1">
-        <v>2338</v>
-      </c>
-      <c r="I106" s="1">
-        <v>6913</v>
-      </c>
-      <c r="J106">
-        <v>0</v>
-      </c>
-      <c r="L106" t="s">
-        <v>44</v>
-      </c>
-      <c r="N106">
-        <v>4475</v>
-      </c>
-    </row>
-    <row r="107" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C107">
-        <v>52.8</v>
-      </c>
-      <c r="E107">
-        <v>52.6</v>
-      </c>
-      <c r="F107" t="s">
-        <v>47</v>
-      </c>
-      <c r="H107">
-        <v>8</v>
-      </c>
-      <c r="I107">
-        <v>-90</v>
-      </c>
-      <c r="J107">
-        <v>-2</v>
-      </c>
-      <c r="K107">
-        <v>10</v>
-      </c>
-      <c r="N107">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="108" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C108">
-        <v>0.2</v>
-      </c>
-      <c r="E108">
-        <f>E104+C108</f>
-      </c>
-    </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A109">
-        <v>25</v>
-      </c>
-      <c r="C109" s="1">
-        <v>2650</v>
-      </c>
-      <c r="E109" s="1">
-        <v>2648</v>
-      </c>
-      <c r="F109" t="s">
-        <v>43</v>
-      </c>
-      <c r="H109" s="1">
-        <v>2386</v>
-      </c>
-      <c r="I109" s="1">
-        <v>6961</v>
-      </c>
-      <c r="J109">
-        <v>0</v>
-      </c>
-      <c r="L109" t="s">
-        <v>44</v>
-      </c>
-      <c r="N109">
-        <v>4575</v>
-      </c>
-    </row>
-    <row r="110" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C110" s="1">
-        <v>2122</v>
-      </c>
-      <c r="E110" s="1">
-        <v>2077</v>
-      </c>
-      <c r="F110" t="s">
-        <v>45</v>
-      </c>
-      <c r="H110" s="1">
-        <v>2362</v>
-      </c>
-      <c r="I110" s="1">
-        <v>6835</v>
-      </c>
-      <c r="J110">
-        <v>2</v>
-      </c>
-      <c r="L110" t="s">
-        <v>46</v>
-      </c>
-      <c r="N110">
-        <v>4475</v>
-      </c>
-    </row>
-    <row r="111" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C111">
-        <v>52.8</v>
-      </c>
-      <c r="E111">
-        <v>57.1</v>
-      </c>
-      <c r="F111" t="s">
-        <v>47</v>
-      </c>
-      <c r="H111">
-        <v>24</v>
-      </c>
-      <c r="I111">
-        <v>126</v>
-      </c>
-      <c r="J111">
-        <v>-2</v>
-      </c>
-      <c r="K111">
-        <v>26</v>
-      </c>
-      <c r="N111">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="112" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C112">
-        <v>-4.3</v>
-      </c>
-      <c r="E112">
-        <f>E108+C112</f>
-      </c>
-    </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A113">
-        <v>26</v>
-      </c>
-      <c r="C113" s="1">
-        <v>2664</v>
-      </c>
-      <c r="E113" s="1">
-        <v>2626</v>
-      </c>
-      <c r="F113" t="s">
-        <v>43</v>
-      </c>
-      <c r="H113" s="1">
-        <v>2400</v>
-      </c>
-      <c r="I113" s="1">
-        <v>6876</v>
-      </c>
-      <c r="J113">
-        <v>-1</v>
-      </c>
-      <c r="L113" t="s">
-        <v>46</v>
-      </c>
-      <c r="N113">
-        <v>4575</v>
-      </c>
-    </row>
-    <row r="114" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C114" s="1">
-        <v>2136</v>
-      </c>
-      <c r="E114" s="1">
-        <v>2127</v>
-      </c>
-      <c r="F114" t="s">
-        <v>45</v>
-      </c>
-      <c r="H114" s="1">
-        <v>2376</v>
-      </c>
-      <c r="I114" s="1">
-        <v>6950</v>
-      </c>
-      <c r="J114">
-        <v>1</v>
-      </c>
-      <c r="L114" t="s">
-        <v>44</v>
-      </c>
-      <c r="N114">
-        <v>4475</v>
-      </c>
-    </row>
-    <row r="115" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C115">
-        <v>52.8</v>
-      </c>
-      <c r="E115">
-        <v>49.9</v>
-      </c>
-      <c r="F115" t="s">
-        <v>47</v>
-      </c>
-      <c r="H115">
-        <v>24</v>
-      </c>
-      <c r="I115">
-        <v>-74</v>
-      </c>
-      <c r="J115">
-        <v>-2</v>
-      </c>
-      <c r="K115">
-        <v>26</v>
-      </c>
-      <c r="N115">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="116" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C116">
-        <v>2.9</v>
-      </c>
-      <c r="E116">
-        <f>E112+C116</f>
-      </c>
-    </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A117">
-        <v>27</v>
-      </c>
-      <c r="C117" s="1">
-        <v>2676</v>
-      </c>
-      <c r="E117" s="1">
-        <v>2637</v>
-      </c>
-      <c r="F117" t="s">
-        <v>43</v>
-      </c>
-      <c r="H117" s="1">
-        <v>2412</v>
-      </c>
-      <c r="I117" s="1">
-        <v>6987</v>
-      </c>
-      <c r="J117">
-        <v>0</v>
-      </c>
-      <c r="L117" t="s">
-        <v>44</v>
-      </c>
-      <c r="N117">
-        <v>4575</v>
-      </c>
-    </row>
-    <row r="118" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C118" s="1">
-        <v>2148</v>
-      </c>
-      <c r="E118" s="1">
-        <v>2139</v>
-      </c>
-      <c r="F118" t="s">
-        <v>45</v>
-      </c>
-      <c r="H118" s="1">
-        <v>2388</v>
-      </c>
-      <c r="I118" s="1">
-        <v>6861</v>
-      </c>
-      <c r="J118">
-        <v>2</v>
-      </c>
-      <c r="L118" t="s">
-        <v>46</v>
-      </c>
-      <c r="N118">
-        <v>4475</v>
-      </c>
-    </row>
-    <row r="119" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C119">
-        <v>52.8</v>
-      </c>
-      <c r="E119">
-        <v>49.8</v>
-      </c>
-      <c r="F119" t="s">
-        <v>47</v>
-      </c>
-      <c r="H119">
-        <v>24</v>
-      </c>
-      <c r="I119">
-        <v>126</v>
-      </c>
-      <c r="J119">
-        <v>-2</v>
-      </c>
-      <c r="K119">
-        <v>26</v>
-      </c>
-      <c r="N119">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="120" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C120">
-        <v>3</v>
-      </c>
-      <c r="E120">
-        <f>E116+C120</f>
-      </c>
-    </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A121">
-        <v>28</v>
-      </c>
-      <c r="C121" s="1">
-        <v>2681</v>
-      </c>
-      <c r="E121" s="1">
-        <v>2674</v>
-      </c>
-      <c r="F121" t="s">
-        <v>43</v>
-      </c>
-      <c r="H121" s="1">
-        <v>2417</v>
-      </c>
-      <c r="I121" s="1">
-        <v>6894</v>
-      </c>
-      <c r="J121">
-        <v>-2</v>
-      </c>
-      <c r="L121" t="s">
-        <v>46</v>
-      </c>
-      <c r="N121">
-        <v>4575</v>
-      </c>
-    </row>
-    <row r="122" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C122" s="1">
-        <v>2153</v>
-      </c>
-      <c r="E122" s="1">
-        <v>2135</v>
-      </c>
-      <c r="F122" t="s">
-        <v>45</v>
-      </c>
-      <c r="H122" s="1">
-        <v>2404</v>
-      </c>
-      <c r="I122" s="1">
-        <v>6979</v>
-      </c>
-      <c r="J122">
-        <v>0</v>
-      </c>
-      <c r="L122" t="s">
-        <v>44</v>
-      </c>
-      <c r="N122">
-        <v>4475</v>
-      </c>
-    </row>
-    <row r="123" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C123">
-        <v>52.8</v>
-      </c>
-      <c r="E123">
-        <v>53.9</v>
-      </c>
-      <c r="F123" t="s">
-        <v>47</v>
-      </c>
-      <c r="H123">
-        <v>13</v>
-      </c>
-      <c r="I123">
-        <v>-85</v>
-      </c>
-      <c r="J123">
-        <v>-2</v>
-      </c>
-      <c r="K123">
-        <v>15</v>
-      </c>
-      <c r="N123">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="124" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C124">
-        <v>-1.1</v>
-      </c>
-      <c r="E124">
-        <f>E120+C124</f>
-      </c>
-    </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A125">
-        <v>29</v>
-      </c>
-      <c r="C125" s="1">
-        <v>2691</v>
-      </c>
-      <c r="E125" s="1">
-        <v>2668</v>
-      </c>
-      <c r="F125" t="s">
-        <v>43</v>
-      </c>
-      <c r="H125" s="1">
-        <v>2427</v>
-      </c>
-      <c r="I125" s="1">
-        <v>7004</v>
-      </c>
-      <c r="J125">
-        <v>-2</v>
-      </c>
-      <c r="L125" t="s">
-        <v>44</v>
-      </c>
-      <c r="N125">
-        <v>4575</v>
-      </c>
-    </row>
-    <row r="126" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C126" s="1">
-        <v>2163</v>
-      </c>
-      <c r="E126" s="1">
-        <v>2157</v>
-      </c>
-      <c r="F126" t="s">
-        <v>45</v>
-      </c>
-      <c r="H126" s="1">
-        <v>2412</v>
-      </c>
-      <c r="I126" s="1">
-        <v>6887</v>
-      </c>
-      <c r="J126">
-        <v>0</v>
-      </c>
-      <c r="L126" t="s">
-        <v>46</v>
-      </c>
-      <c r="N126">
-        <v>4475</v>
-      </c>
-    </row>
-    <row r="127" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C127">
-        <v>52.8</v>
-      </c>
-      <c r="E127">
-        <v>51.1</v>
-      </c>
-      <c r="F127" t="s">
-        <v>47</v>
-      </c>
-      <c r="H127">
-        <v>15</v>
-      </c>
-      <c r="I127">
-        <v>117</v>
-      </c>
-      <c r="J127">
-        <v>-2</v>
-      </c>
-      <c r="K127">
-        <v>17</v>
-      </c>
-      <c r="N127">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="128" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C128">
-        <v>1.7</v>
-      </c>
-      <c r="E128">
-        <f>E124+C128</f>
-      </c>
-    </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A129">
-        <v>30</v>
-      </c>
-      <c r="C129" s="1">
-        <v>2710</v>
-      </c>
-      <c r="E129" s="1">
-        <v>2710</v>
-      </c>
-      <c r="F129" t="s">
-        <v>43</v>
-      </c>
-      <c r="H129" s="1">
-        <v>2446</v>
-      </c>
-      <c r="I129" s="1">
-        <v>6921</v>
-      </c>
-      <c r="J129">
-        <v>0</v>
-      </c>
-      <c r="L129" t="s">
-        <v>46</v>
-      </c>
-      <c r="N129">
-        <v>4575</v>
-      </c>
-    </row>
-    <row r="130" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C130" s="1">
-        <v>2182</v>
-      </c>
-      <c r="E130" s="1">
-        <v>2154</v>
-      </c>
-      <c r="F130" t="s">
-        <v>45</v>
-      </c>
-      <c r="H130" s="1">
-        <v>2432</v>
-      </c>
-      <c r="I130" s="1">
-        <v>7005</v>
-      </c>
-      <c r="J130">
-        <v>2</v>
-      </c>
-      <c r="L130" t="s">
-        <v>44</v>
-      </c>
-      <c r="N130">
-        <v>4475</v>
-      </c>
-    </row>
-    <row r="131" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C131">
-        <v>52.8</v>
-      </c>
-      <c r="E131">
-        <v>55.6</v>
-      </c>
-      <c r="F131" t="s">
-        <v>47</v>
-      </c>
-      <c r="H131">
-        <v>14</v>
-      </c>
-      <c r="I131">
-        <v>-84</v>
-      </c>
-      <c r="J131">
-        <v>-2</v>
-      </c>
-      <c r="K131">
-        <v>16</v>
-      </c>
-      <c r="N131">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="132" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C132">
-        <v>-2.8</v>
-      </c>
-      <c r="E132">
-        <f>E128+C132</f>
-      </c>
-    </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A133">
-        <v>31</v>
-      </c>
-      <c r="C133" s="1">
-        <v>2725</v>
-      </c>
-      <c r="E133" s="1">
-        <v>2697</v>
-      </c>
-      <c r="F133" t="s">
-        <v>43</v>
-      </c>
-      <c r="H133" s="1">
-        <v>2461</v>
-      </c>
-      <c r="I133" s="1">
-        <v>7037</v>
-      </c>
-      <c r="J133">
-        <v>-1</v>
-      </c>
-      <c r="L133" t="s">
-        <v>44</v>
-      </c>
-      <c r="N133">
-        <v>4575</v>
-      </c>
-    </row>
-    <row r="134" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C134" s="1">
-        <v>2197</v>
-      </c>
-      <c r="E134" s="1">
-        <v>2210</v>
-      </c>
-      <c r="F134" t="s">
-        <v>45</v>
-      </c>
-      <c r="H134" s="1">
-        <v>2453</v>
-      </c>
-      <c r="I134" s="1">
-        <v>6927</v>
-      </c>
-      <c r="J134">
-        <v>1</v>
-      </c>
-      <c r="L134" t="s">
-        <v>46</v>
-      </c>
-      <c r="N134">
-        <v>4475</v>
-      </c>
-    </row>
-    <row r="135" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C135">
-        <v>52.8</v>
-      </c>
-      <c r="E135">
-        <v>48.7</v>
-      </c>
-      <c r="F135" t="s">
-        <v>47</v>
-      </c>
-      <c r="H135">
-        <v>8</v>
-      </c>
-      <c r="I135">
-        <v>110</v>
-      </c>
-      <c r="J135">
-        <v>-2</v>
-      </c>
-      <c r="K135">
-        <v>10</v>
-      </c>
-      <c r="N135">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="136" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C136">
-        <v>4.1</v>
-      </c>
-      <c r="E136">
-        <f>E132+C136</f>
-      </c>
-    </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A137">
-        <v>32</v>
-      </c>
-      <c r="C137" s="1">
-        <v>2746</v>
-      </c>
-      <c r="E137" s="1">
-        <v>2736</v>
-      </c>
-      <c r="F137" t="s">
-        <v>43</v>
-      </c>
-      <c r="H137" s="1">
-        <v>2482</v>
-      </c>
-      <c r="I137" s="1">
-        <v>6958</v>
-      </c>
-      <c r="J137">
-        <v>-1</v>
-      </c>
-      <c r="L137" t="s">
-        <v>46</v>
-      </c>
-      <c r="N137">
-        <v>4575</v>
-      </c>
-    </row>
-    <row r="138" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C138" s="1">
-        <v>2218</v>
-      </c>
-      <c r="E138" s="1">
-        <v>2199</v>
-      </c>
-      <c r="F138" t="s">
-        <v>45</v>
-      </c>
-      <c r="H138" s="1">
-        <v>2467</v>
-      </c>
-      <c r="I138" s="1">
-        <v>7041</v>
-      </c>
-      <c r="J138">
-        <v>1</v>
-      </c>
-      <c r="L138" t="s">
-        <v>44</v>
-      </c>
-      <c r="N138">
-        <v>4475</v>
-      </c>
-    </row>
-    <row r="139" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C139">
-        <v>52.8</v>
-      </c>
-      <c r="E139">
-        <v>53.7</v>
-      </c>
-      <c r="F139" t="s">
-        <v>47</v>
-      </c>
-      <c r="H139">
-        <v>15</v>
-      </c>
-      <c r="I139">
-        <v>-83</v>
-      </c>
-      <c r="J139">
-        <v>-2</v>
-      </c>
-      <c r="K139">
-        <v>17</v>
-      </c>
-      <c r="N139">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="140" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C140">
-        <v>-0.9</v>
-      </c>
-      <c r="E140">
-        <f>E136+C140</f>
-      </c>
-    </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A141">
-        <v>33</v>
-      </c>
-      <c r="C141" s="1">
-        <v>2746</v>
-      </c>
-      <c r="E141" s="1">
-        <v>2746</v>
-      </c>
-      <c r="F141" t="s">
-        <v>43</v>
-      </c>
-      <c r="H141" s="1">
-        <v>2482</v>
-      </c>
-      <c r="I141" s="1">
-        <v>7058</v>
-      </c>
-      <c r="J141">
-        <v>-1</v>
-      </c>
-      <c r="L141" t="s">
-        <v>44</v>
-      </c>
-      <c r="N141">
-        <v>4575</v>
-      </c>
-    </row>
-    <row r="142" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C142" s="1">
-        <v>2218</v>
-      </c>
-      <c r="E142" s="1">
-        <v>2204</v>
-      </c>
-      <c r="F142" t="s">
-        <v>45</v>
-      </c>
-      <c r="H142" s="1">
-        <v>2475</v>
-      </c>
-      <c r="I142" s="1">
-        <v>6949</v>
-      </c>
-      <c r="J142">
-        <v>1</v>
-      </c>
-      <c r="L142" t="s">
-        <v>46</v>
-      </c>
-      <c r="N142">
-        <v>4475</v>
-      </c>
-    </row>
-    <row r="143" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C143">
-        <v>52.8</v>
-      </c>
-      <c r="E143">
-        <v>54.2</v>
-      </c>
-      <c r="F143" t="s">
-        <v>47</v>
-      </c>
-      <c r="H143">
-        <v>7</v>
-      </c>
-      <c r="I143">
-        <v>109</v>
-      </c>
-      <c r="J143">
-        <v>-2</v>
-      </c>
-      <c r="K143">
-        <v>9</v>
-      </c>
-      <c r="N143">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="144" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C144">
-        <v>-1.4</v>
-      </c>
-      <c r="E144">
-        <f>E140+C144</f>
-      </c>
-    </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A145">
-        <v>34</v>
-      </c>
-      <c r="C145" s="1">
-        <v>2769</v>
-      </c>
-      <c r="E145" s="1">
-        <v>2744</v>
-      </c>
-      <c r="F145" t="s">
-        <v>43</v>
-      </c>
-      <c r="H145" s="1">
-        <v>2505</v>
-      </c>
-      <c r="I145" s="1">
-        <v>6981</v>
-      </c>
-      <c r="J145">
-        <v>-1</v>
-      </c>
-      <c r="L145" t="s">
-        <v>46</v>
-      </c>
-      <c r="N145">
-        <v>4575</v>
-      </c>
-    </row>
-    <row r="146" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C146" s="1">
-        <v>2241</v>
-      </c>
-      <c r="E146" s="1">
-        <v>2235</v>
-      </c>
-      <c r="F146" t="s">
-        <v>45</v>
-      </c>
-      <c r="H146" s="1">
-        <v>2489</v>
-      </c>
-      <c r="I146" s="1">
-        <v>7063</v>
-      </c>
-      <c r="J146">
-        <v>1</v>
-      </c>
-      <c r="L146" t="s">
-        <v>44</v>
-      </c>
-      <c r="N146">
-        <v>4475</v>
-      </c>
-    </row>
-    <row r="147" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C147">
-        <v>52.8</v>
-      </c>
-      <c r="E147">
-        <v>50.9</v>
-      </c>
-      <c r="F147" t="s">
-        <v>47</v>
-      </c>
-      <c r="H147">
-        <v>16</v>
-      </c>
-      <c r="I147">
-        <v>-82</v>
-      </c>
-      <c r="J147">
-        <v>-2</v>
-      </c>
-      <c r="K147">
-        <v>18</v>
-      </c>
-      <c r="N147">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="148" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C148">
-        <v>1.9</v>
-      </c>
-      <c r="E148">
-        <f>E144+C148</f>
-      </c>
-    </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A149" t="s">
-        <v>48</v>
-      </c>
-      <c r="C149">
-        <v>85640</v>
-      </c>
-      <c r="E149">
-        <v>85127</v>
-      </c>
-      <c r="F149" t="s">
-        <v>43</v>
-      </c>
-      <c r="H149">
-        <v>76664</v>
-      </c>
-      <c r="I149">
-        <v>230546</v>
-      </c>
-      <c r="J149">
-        <v>-32</v>
-      </c>
-    </row>
-    <row r="150" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C150">
-        <v>67688</v>
-      </c>
-      <c r="E150">
-        <v>67146</v>
-      </c>
-      <c r="F150" t="s">
-        <v>45</v>
-      </c>
-      <c r="H150">
-        <v>76127</v>
-      </c>
-      <c r="I150">
-        <v>229941</v>
-      </c>
-      <c r="J150">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="151" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C151">
-        <v>1794.9</v>
-      </c>
-      <c r="E151">
-        <v>1798.1</v>
-      </c>
-      <c r="F151" t="s">
-        <v>47</v>
-      </c>
-      <c r="H151">
-        <v>537</v>
-      </c>
-      <c r="I151">
-        <v>605</v>
-      </c>
-      <c r="J151">
-        <v>-68</v>
-      </c>
-      <c r="K151">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="152" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C152">
-        <v>-3.199999999999818</v>
-      </c>
-      <c r="E152">
         <v>-3.199999999999818</v>
       </c>
     </row>

--- a/So_do_(tên_mốc_mua).xlsx
+++ b/So_do_(tên_mốc_mua).xlsx
@@ -731,19 +731,19 @@
         <v>1</v>
       </c>
       <c r="C13" s="1">
-        <v>2462</v>
+        <v>2426</v>
       </c>
       <c r="E13" s="1">
-        <v>2429</v>
+        <v>2430</v>
       </c>
       <c r="F13" t="s">
         <v>43</v>
       </c>
       <c r="H13" s="1">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="I13" s="1">
-        <v>6586</v>
+        <v>6587</v>
       </c>
       <c r="J13">
         <v>1</v>
@@ -757,22 +757,22 @@
     </row>
     <row r="14" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C14" s="1">
-        <v>1562</v>
+        <v>1601</v>
       </c>
       <c r="E14" s="1">
-        <v>1479</v>
+        <v>1615</v>
       </c>
       <c r="F14" t="s">
         <v>45</v>
       </c>
       <c r="H14" s="1">
-        <v>1954</v>
+        <v>2021</v>
       </c>
       <c r="I14" s="1">
-        <v>6427</v>
+        <v>6497</v>
       </c>
       <c r="J14">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L14" t="s">
         <v>46</v>
@@ -783,25 +783,25 @@
     </row>
     <row r="15" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C15">
-        <v>90</v>
+        <v>82.5</v>
       </c>
       <c r="E15">
-        <v>95</v>
+        <v>81.5</v>
       </c>
       <c r="F15" t="s">
         <v>47</v>
       </c>
       <c r="H15">
-        <v>58</v>
+        <v>-8</v>
       </c>
       <c r="I15">
-        <v>159</v>
+        <v>90</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="K15">
-        <v>59</v>
+        <v>-10</v>
       </c>
       <c r="N15">
         <v>100</v>
@@ -809,10 +809,10 @@
     </row>
     <row r="16" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C16">
-        <v>-5</v>
+        <v>1</v>
       </c>
       <c r="E16">
-        <v>-5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
@@ -820,22 +820,22 @@
         <v>2</v>
       </c>
       <c r="C17" s="1">
-        <v>2390</v>
+        <v>2468</v>
       </c>
       <c r="E17" s="1">
-        <v>2440</v>
+        <v>2481</v>
       </c>
       <c r="F17" t="s">
         <v>43</v>
       </c>
       <c r="H17" s="1">
-        <v>1950</v>
+        <v>2032</v>
       </c>
       <c r="I17" s="1">
-        <v>6425</v>
+        <v>6509</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L17" t="s">
         <v>46</v>
@@ -846,22 +846,22 @@
     </row>
     <row r="18" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C18" s="1">
-        <v>1507</v>
+        <v>1594</v>
       </c>
       <c r="E18" s="1">
-        <v>1507</v>
+        <v>1593</v>
       </c>
       <c r="F18" t="s">
         <v>45</v>
       </c>
       <c r="H18" s="1">
-        <v>1975</v>
+        <v>2038</v>
       </c>
       <c r="I18" s="1">
-        <v>6548</v>
+        <v>6613</v>
       </c>
       <c r="J18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L18" t="s">
         <v>44</v>
@@ -872,25 +872,25 @@
     </row>
     <row r="19" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C19">
-        <v>88.3</v>
+        <v>87.4</v>
       </c>
       <c r="E19">
-        <v>93.3</v>
+        <v>88.8</v>
       </c>
       <c r="F19" t="s">
         <v>47</v>
       </c>
       <c r="H19">
-        <v>-25</v>
+        <v>-6</v>
       </c>
       <c r="I19">
-        <v>-123</v>
+        <v>-104</v>
       </c>
       <c r="J19">
         <v>-2</v>
       </c>
       <c r="K19">
-        <v>-23</v>
+        <v>-4</v>
       </c>
       <c r="N19">
         <v>100</v>
@@ -898,7 +898,7 @@
     </row>
     <row r="20" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C20">
-        <v>-5</v>
+        <v>-1.4</v>
       </c>
       <c r="E20">
         <f>E16+C20</f>
@@ -909,22 +909,22 @@
         <v>3</v>
       </c>
       <c r="C21" s="1">
-        <v>2426</v>
+        <v>2538</v>
       </c>
       <c r="E21" s="1">
-        <v>2409</v>
+        <v>2488</v>
       </c>
       <c r="F21" t="s">
         <v>43</v>
       </c>
       <c r="H21" s="1">
-        <v>2025</v>
+        <v>2111</v>
       </c>
       <c r="I21" s="1">
-        <v>6599</v>
+        <v>6686</v>
       </c>
       <c r="J21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" t="s">
         <v>44</v>
@@ -935,22 +935,22 @@
     </row>
     <row r="22" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C22" s="1">
-        <v>1626</v>
+        <v>1680</v>
       </c>
       <c r="E22" s="1">
-        <v>1559</v>
+        <v>1621</v>
       </c>
       <c r="F22" t="s">
         <v>45</v>
       </c>
       <c r="H22" s="1">
-        <v>1982</v>
+        <v>2056</v>
       </c>
       <c r="I22" s="1">
-        <v>6458</v>
+        <v>6533</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="L22" t="s">
         <v>46</v>
@@ -961,25 +961,25 @@
     </row>
     <row r="23" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C23">
-        <v>80</v>
+        <v>85.8</v>
       </c>
       <c r="E23">
-        <v>85</v>
+        <v>86.7</v>
       </c>
       <c r="F23" t="s">
         <v>47</v>
       </c>
       <c r="H23">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="I23">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="J23">
         <v>2</v>
       </c>
       <c r="K23">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="N23">
         <v>100</v>
@@ -987,7 +987,7 @@
     </row>
     <row r="24" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C24">
-        <v>-5</v>
+        <v>-0.9</v>
       </c>
       <c r="E24">
         <f>E20+C24</f>
@@ -998,19 +998,19 @@
         <v>4</v>
       </c>
       <c r="C25" s="1">
-        <v>2422</v>
+        <v>2601</v>
       </c>
       <c r="E25" s="1">
-        <v>2475</v>
+        <v>2496</v>
       </c>
       <c r="F25" t="s">
         <v>43</v>
       </c>
       <c r="H25" s="1">
-        <v>1973</v>
+        <v>2185</v>
       </c>
       <c r="I25" s="1">
-        <v>6449</v>
+        <v>6661</v>
       </c>
       <c r="J25">
         <v>-1</v>
@@ -1024,19 +1024,19 @@
     </row>
     <row r="26" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C26" s="1">
-        <v>1522</v>
+        <v>1770</v>
       </c>
       <c r="E26" s="1">
-        <v>1525</v>
+        <v>1658</v>
       </c>
       <c r="F26" t="s">
         <v>45</v>
       </c>
       <c r="H26" s="1">
-        <v>2000</v>
+        <v>2075</v>
       </c>
       <c r="I26" s="1">
-        <v>6574</v>
+        <v>6649</v>
       </c>
       <c r="J26">
         <v>1</v>
@@ -1050,25 +1050,25 @@
     </row>
     <row r="27" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C27">
-        <v>90</v>
+        <v>83.1</v>
       </c>
       <c r="E27">
-        <v>95</v>
+        <v>83.8</v>
       </c>
       <c r="F27" t="s">
         <v>47</v>
       </c>
       <c r="H27">
-        <v>-27</v>
+        <v>110</v>
       </c>
       <c r="I27">
-        <v>-125</v>
+        <v>12</v>
       </c>
       <c r="J27">
         <v>-2</v>
       </c>
       <c r="K27">
-        <v>-25</v>
+        <v>112</v>
       </c>
       <c r="N27">
         <v>100</v>
@@ -1076,7 +1076,7 @@
     </row>
     <row r="28" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C28">
-        <v>-5</v>
+        <v>-0.7</v>
       </c>
       <c r="E28">
         <f>E24+C28</f>
@@ -1087,22 +1087,22 @@
         <v>5</v>
       </c>
       <c r="C29" s="1">
-        <v>2503</v>
+        <v>2497</v>
       </c>
       <c r="E29" s="1">
-        <v>2497</v>
+        <v>2515</v>
       </c>
       <c r="F29" t="s">
         <v>43</v>
       </c>
       <c r="H29" s="1">
-        <v>2052</v>
+        <v>2081</v>
       </c>
       <c r="I29" s="1">
-        <v>6627</v>
+        <v>6655</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" t="s">
         <v>44</v>
@@ -1113,22 +1113,22 @@
     </row>
     <row r="30" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C30" s="1">
-        <v>1603</v>
+        <v>1662</v>
       </c>
       <c r="E30" s="1">
-        <v>1547</v>
+        <v>1658</v>
       </c>
       <c r="F30" t="s">
         <v>45</v>
       </c>
       <c r="H30" s="1">
-        <v>2022</v>
+        <v>2088</v>
       </c>
       <c r="I30" s="1">
-        <v>6499</v>
+        <v>6564</v>
       </c>
       <c r="J30">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L30" t="s">
         <v>46</v>
@@ -1139,25 +1139,25 @@
     </row>
     <row r="31" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C31">
-        <v>90</v>
+        <v>83.5</v>
       </c>
       <c r="E31">
-        <v>95</v>
+        <v>85.7</v>
       </c>
       <c r="F31" t="s">
         <v>47</v>
       </c>
       <c r="H31">
-        <v>30</v>
+        <v>-7</v>
       </c>
       <c r="I31">
-        <v>128</v>
+        <v>91</v>
       </c>
       <c r="J31">
         <v>2</v>
       </c>
       <c r="K31">
-        <v>28</v>
+        <v>-9</v>
       </c>
       <c r="N31">
         <v>100</v>
@@ -1165,7 +1165,7 @@
     </row>
     <row r="32" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C32">
-        <v>-5</v>
+        <v>-2.2</v>
       </c>
       <c r="E32">
         <f>E28+C32</f>
@@ -1176,22 +1176,22 @@
         <v>6</v>
       </c>
       <c r="C33" s="1">
+        <v>2523</v>
+      </c>
+      <c r="E33" s="1">
         <v>2532</v>
-      </c>
-      <c r="E33" s="1">
-        <v>2480</v>
       </c>
       <c r="F33" t="s">
         <v>43</v>
       </c>
       <c r="H33" s="1">
-        <v>2102</v>
+        <v>2096</v>
       </c>
       <c r="I33" s="1">
-        <v>6577</v>
+        <v>6573</v>
       </c>
       <c r="J33">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L33" t="s">
         <v>46</v>
@@ -1202,22 +1202,22 @@
     </row>
     <row r="34" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C34" s="1">
-        <v>1672</v>
+        <v>1670</v>
       </c>
       <c r="E34" s="1">
-        <v>1598</v>
+        <v>1676</v>
       </c>
       <c r="F34" t="s">
         <v>45</v>
       </c>
       <c r="H34" s="1">
-        <v>2040</v>
+        <v>2104</v>
       </c>
       <c r="I34" s="1">
-        <v>6613</v>
+        <v>6679</v>
       </c>
       <c r="J34">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L34" t="s">
         <v>44</v>
@@ -1228,25 +1228,25 @@
     </row>
     <row r="35" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C35">
-        <v>86</v>
+        <v>85.3</v>
       </c>
       <c r="E35">
-        <v>88.2</v>
+        <v>85.6</v>
       </c>
       <c r="F35" t="s">
         <v>47</v>
       </c>
       <c r="H35">
-        <v>62</v>
+        <v>-8</v>
       </c>
       <c r="I35">
-        <v>-36</v>
+        <v>-106</v>
       </c>
       <c r="J35">
         <v>-2</v>
       </c>
       <c r="K35">
-        <v>64</v>
+        <v>-6</v>
       </c>
       <c r="N35">
         <v>100</v>
@@ -1254,7 +1254,7 @@
     </row>
     <row r="36" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C36">
-        <v>-2.2</v>
+        <v>-0.3</v>
       </c>
       <c r="E36">
         <f>E32+C36</f>
@@ -1265,22 +1265,22 @@
         <v>7</v>
       </c>
       <c r="C37" s="1">
-        <v>2487</v>
+        <v>2545</v>
       </c>
       <c r="E37" s="1">
-        <v>2497</v>
+        <v>2556</v>
       </c>
       <c r="F37" t="s">
         <v>43</v>
       </c>
       <c r="H37" s="1">
-        <v>2038</v>
+        <v>2118</v>
       </c>
       <c r="I37" s="1">
-        <v>6612</v>
+        <v>6693</v>
       </c>
       <c r="J37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L37" t="s">
         <v>44</v>
@@ -1291,22 +1291,22 @@
     </row>
     <row r="38" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C38" s="1">
-        <v>1587</v>
+        <v>1691</v>
       </c>
       <c r="E38" s="1">
-        <v>1597</v>
+        <v>1699</v>
       </c>
       <c r="F38" t="s">
         <v>45</v>
       </c>
       <c r="H38" s="1">
-        <v>2047</v>
+        <v>2127</v>
       </c>
       <c r="I38" s="1">
-        <v>6523</v>
+        <v>6604</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="L38" t="s">
         <v>46</v>
@@ -1317,10 +1317,10 @@
     </row>
     <row r="39" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C39">
-        <v>90</v>
+        <v>85.4</v>
       </c>
       <c r="E39">
-        <v>90</v>
+        <v>85.7</v>
       </c>
       <c r="F39" t="s">
         <v>47</v>
@@ -1343,7 +1343,7 @@
     </row>
     <row r="40" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C40">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="E40">
         <f>E36+C40</f>
@@ -1354,19 +1354,19 @@
         <v>8</v>
       </c>
       <c r="C41" s="1">
-        <v>2493</v>
+        <v>2579</v>
       </c>
       <c r="E41" s="1">
-        <v>2444</v>
+        <v>2593</v>
       </c>
       <c r="F41" t="s">
         <v>43</v>
       </c>
       <c r="H41" s="1">
-        <v>2095</v>
+        <v>2143</v>
       </c>
       <c r="I41" s="1">
-        <v>6572</v>
+        <v>6620</v>
       </c>
       <c r="J41">
         <v>-2</v>
@@ -1380,19 +1380,19 @@
     </row>
     <row r="42" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C42" s="1">
-        <v>1693</v>
+        <v>1702</v>
       </c>
       <c r="E42" s="1">
-        <v>1675</v>
+        <v>1700</v>
       </c>
       <c r="F42" t="s">
         <v>45</v>
       </c>
       <c r="H42" s="1">
-        <v>2061</v>
+        <v>2148</v>
       </c>
       <c r="I42" s="1">
-        <v>6636</v>
+        <v>6723</v>
       </c>
       <c r="J42">
         <v>0</v>
@@ -1406,25 +1406,25 @@
     </row>
     <row r="43" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C43">
-        <v>80</v>
+        <v>87.7</v>
       </c>
       <c r="E43">
-        <v>76.9</v>
+        <v>89.3</v>
       </c>
       <c r="F43" t="s">
         <v>47</v>
       </c>
       <c r="H43">
-        <v>34</v>
+        <v>-5</v>
       </c>
       <c r="I43">
-        <v>-64</v>
+        <v>-103</v>
       </c>
       <c r="J43">
         <v>-2</v>
       </c>
       <c r="K43">
-        <v>36</v>
+        <v>-3</v>
       </c>
       <c r="N43">
         <v>100</v>
@@ -1432,7 +1432,7 @@
     </row>
     <row r="44" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C44">
-        <v>3.1</v>
+        <v>-1.6</v>
       </c>
       <c r="E44">
         <f>E40+C44</f>
@@ -1443,22 +1443,22 @@
         <v>9</v>
       </c>
       <c r="C45" s="1">
-        <v>2511</v>
+        <v>2755</v>
       </c>
       <c r="E45" s="1">
-        <v>2466</v>
+        <v>2581</v>
       </c>
       <c r="F45" t="s">
         <v>43</v>
       </c>
       <c r="H45" s="1">
-        <v>2112</v>
+        <v>2317</v>
       </c>
       <c r="I45" s="1">
-        <v>6687</v>
+        <v>6891</v>
       </c>
       <c r="J45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" t="s">
         <v>44</v>
@@ -1469,22 +1469,22 @@
     </row>
     <row r="46" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C46" s="1">
-        <v>1711</v>
+        <v>1883</v>
       </c>
       <c r="E46" s="1">
-        <v>1671</v>
+        <v>1732</v>
       </c>
       <c r="F46" t="s">
         <v>45</v>
       </c>
       <c r="H46" s="1">
-        <v>2069</v>
+        <v>2156</v>
       </c>
       <c r="I46" s="1">
-        <v>6546</v>
+        <v>6632</v>
       </c>
       <c r="J46">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L46" t="s">
         <v>46</v>
@@ -1495,25 +1495,25 @@
     </row>
     <row r="47" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C47">
-        <v>80</v>
+        <v>87.2</v>
       </c>
       <c r="E47">
-        <v>79.5</v>
+        <v>84.9</v>
       </c>
       <c r="F47" t="s">
         <v>47</v>
       </c>
       <c r="H47">
-        <v>43</v>
+        <v>161</v>
       </c>
       <c r="I47">
-        <v>141</v>
+        <v>259</v>
       </c>
       <c r="J47">
         <v>2</v>
       </c>
       <c r="K47">
-        <v>41</v>
+        <v>159</v>
       </c>
       <c r="N47">
         <v>100</v>
@@ -1521,7 +1521,7 @@
     </row>
     <row r="48" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C48">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="E48">
         <f>E44+C48</f>
@@ -1532,22 +1532,22 @@
         <v>10</v>
       </c>
       <c r="C49" s="1">
-        <v>2595</v>
+        <v>2594</v>
       </c>
       <c r="E49" s="1">
-        <v>2527</v>
+        <v>2590</v>
       </c>
       <c r="F49" t="s">
         <v>43</v>
       </c>
       <c r="H49" s="1">
-        <v>2143</v>
+        <v>2166</v>
       </c>
       <c r="I49" s="1">
-        <v>6618</v>
+        <v>6643</v>
       </c>
       <c r="J49">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L49" t="s">
         <v>46</v>
@@ -1558,22 +1558,22 @@
     </row>
     <row r="50" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C50" s="1">
-        <v>1695</v>
+        <v>1741</v>
       </c>
       <c r="E50" s="1">
-        <v>1658</v>
+        <v>1751</v>
       </c>
       <c r="F50" t="s">
         <v>45</v>
       </c>
       <c r="H50" s="1">
-        <v>2092</v>
+        <v>2169</v>
       </c>
       <c r="I50" s="1">
-        <v>6665</v>
+        <v>6744</v>
       </c>
       <c r="J50">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L50" t="s">
         <v>44</v>
@@ -1584,25 +1584,25 @@
     </row>
     <row r="51" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C51">
-        <v>90</v>
+        <v>85.3</v>
       </c>
       <c r="E51">
-        <v>86.9</v>
+        <v>83.9</v>
       </c>
       <c r="F51" t="s">
         <v>47</v>
       </c>
       <c r="H51">
-        <v>51</v>
+        <v>-3</v>
       </c>
       <c r="I51">
-        <v>-47</v>
+        <v>-101</v>
       </c>
       <c r="J51">
         <v>-2</v>
       </c>
       <c r="K51">
-        <v>53</v>
+        <v>-1</v>
       </c>
       <c r="N51">
         <v>100</v>
@@ -1610,7 +1610,7 @@
     </row>
     <row r="52" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C52">
-        <v>3.1</v>
+        <v>1.4</v>
       </c>
       <c r="E52">
         <f>E48+C52</f>
@@ -1621,22 +1621,22 @@
         <v>11</v>
       </c>
       <c r="C53" s="1">
-        <v>2519</v>
+        <v>2712</v>
       </c>
       <c r="E53" s="1">
-        <v>2492</v>
+        <v>2608</v>
       </c>
       <c r="F53" t="s">
         <v>43</v>
       </c>
       <c r="H53" s="1">
-        <v>2118</v>
+        <v>2295</v>
       </c>
       <c r="I53" s="1">
-        <v>6691</v>
+        <v>6872</v>
       </c>
       <c r="J53">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L53" t="s">
         <v>44</v>
@@ -1647,22 +1647,22 @@
     </row>
     <row r="54" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C54" s="1">
-        <v>1719</v>
+        <v>1876</v>
       </c>
       <c r="E54" s="1">
-        <v>1712</v>
+        <v>1749</v>
       </c>
       <c r="F54" t="s">
         <v>45</v>
       </c>
       <c r="H54" s="1">
-        <v>2101</v>
+        <v>2180</v>
       </c>
       <c r="I54" s="1">
-        <v>6576</v>
+        <v>6656</v>
       </c>
       <c r="J54">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L54" t="s">
         <v>46</v>
@@ -1673,25 +1673,25 @@
     </row>
     <row r="55" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C55">
-        <v>80</v>
+        <v>83.6</v>
       </c>
       <c r="E55">
-        <v>78</v>
+        <v>85.9</v>
       </c>
       <c r="F55" t="s">
         <v>47</v>
       </c>
       <c r="H55">
-        <v>17</v>
+        <v>115</v>
       </c>
       <c r="I55">
-        <v>115</v>
+        <v>216</v>
       </c>
       <c r="J55">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="K55">
-        <v>15</v>
+        <v>116</v>
       </c>
       <c r="N55">
         <v>100</v>
@@ -1699,7 +1699,7 @@
     </row>
     <row r="56" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C56">
-        <v>2</v>
+        <v>-2.3</v>
       </c>
       <c r="E56">
         <f>E52+C56</f>
@@ -1710,22 +1710,22 @@
         <v>12</v>
       </c>
       <c r="C57" s="1">
-        <v>2561</v>
+        <v>2622</v>
       </c>
       <c r="E57" s="1">
-        <v>2517</v>
+        <v>2633</v>
       </c>
       <c r="F57" t="s">
         <v>43</v>
       </c>
       <c r="H57" s="1">
-        <v>2162</v>
+        <v>2197</v>
       </c>
       <c r="I57" s="1">
-        <v>6639</v>
+        <v>6673</v>
       </c>
       <c r="J57">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L57" t="s">
         <v>46</v>
@@ -1736,22 +1736,22 @@
     </row>
     <row r="58" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C58" s="1">
-        <v>1761</v>
+        <v>1774</v>
       </c>
       <c r="E58" s="1">
-        <v>1727</v>
+        <v>1770</v>
       </c>
       <c r="F58" t="s">
         <v>45</v>
       </c>
       <c r="H58" s="1">
-        <v>2123</v>
+        <v>2201</v>
       </c>
       <c r="I58" s="1">
-        <v>6698</v>
+        <v>6775</v>
       </c>
       <c r="J58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58" t="s">
         <v>44</v>
@@ -1762,25 +1762,25 @@
     </row>
     <row r="59" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C59">
-        <v>80</v>
+        <v>84.8</v>
       </c>
       <c r="E59">
-        <v>79</v>
+        <v>86.3</v>
       </c>
       <c r="F59" t="s">
         <v>47</v>
       </c>
       <c r="H59">
-        <v>39</v>
+        <v>-4</v>
       </c>
       <c r="I59">
-        <v>-59</v>
+        <v>-102</v>
       </c>
       <c r="J59">
         <v>-2</v>
       </c>
       <c r="K59">
-        <v>41</v>
+        <v>-2</v>
       </c>
       <c r="N59">
         <v>100</v>
@@ -1788,7 +1788,7 @@
     </row>
     <row r="60" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C60">
-        <v>1</v>
+        <v>-1.5</v>
       </c>
       <c r="E60">
         <f>E56+C60</f>
@@ -1799,19 +1799,19 @@
         <v>13</v>
       </c>
       <c r="C61" s="1">
-        <v>2582</v>
+        <v>2848</v>
       </c>
       <c r="E61" s="1">
-        <v>2599</v>
+        <v>2656</v>
       </c>
       <c r="F61" t="s">
         <v>43</v>
       </c>
       <c r="H61" s="1">
-        <v>2132</v>
+        <v>2409</v>
       </c>
       <c r="I61" s="1">
-        <v>6705</v>
+        <v>6982</v>
       </c>
       <c r="J61">
         <v>2</v>
@@ -1825,19 +1825,19 @@
     </row>
     <row r="62" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C62" s="1">
-        <v>1682</v>
+        <v>1972</v>
       </c>
       <c r="E62" s="1">
-        <v>1685</v>
+        <v>1785</v>
       </c>
       <c r="F62" t="s">
         <v>45</v>
       </c>
       <c r="H62" s="1">
-        <v>2141</v>
+        <v>2219</v>
       </c>
       <c r="I62" s="1">
-        <v>6616</v>
+        <v>6694</v>
       </c>
       <c r="J62">
         <v>0</v>
@@ -1851,25 +1851,25 @@
     </row>
     <row r="63" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C63">
-        <v>90</v>
+        <v>87.6</v>
       </c>
       <c r="E63">
-        <v>91.4</v>
+        <v>87.1</v>
       </c>
       <c r="F63" t="s">
         <v>47</v>
       </c>
       <c r="H63">
-        <v>-9</v>
+        <v>190</v>
       </c>
       <c r="I63">
-        <v>89</v>
+        <v>288</v>
       </c>
       <c r="J63">
         <v>2</v>
       </c>
       <c r="K63">
-        <v>-11</v>
+        <v>188</v>
       </c>
       <c r="N63">
         <v>100</v>
@@ -1877,7 +1877,7 @@
     </row>
     <row r="64" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C64">
-        <v>-1.4</v>
+        <v>0.5</v>
       </c>
       <c r="E64">
         <f>E60+C64</f>
@@ -1888,19 +1888,19 @@
         <v>14</v>
       </c>
       <c r="C65" s="1">
-        <v>2632</v>
+        <v>2667</v>
       </c>
       <c r="E65" s="1">
-        <v>2597</v>
+        <v>2680</v>
       </c>
       <c r="F65" t="s">
         <v>43</v>
       </c>
       <c r="H65" s="1">
-        <v>2182</v>
+        <v>2230</v>
       </c>
       <c r="I65" s="1">
-        <v>6659</v>
+        <v>6707</v>
       </c>
       <c r="J65">
         <v>-2</v>
@@ -1914,19 +1914,19 @@
     </row>
     <row r="66" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C66" s="1">
-        <v>1732</v>
+        <v>1796</v>
       </c>
       <c r="E66" s="1">
-        <v>1703</v>
+        <v>1798</v>
       </c>
       <c r="F66" t="s">
         <v>45</v>
       </c>
       <c r="H66" s="1">
-        <v>2150</v>
+        <v>2237</v>
       </c>
       <c r="I66" s="1">
-        <v>6725</v>
+        <v>6812</v>
       </c>
       <c r="J66">
         <v>0</v>
@@ -1940,25 +1940,25 @@
     </row>
     <row r="67" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C67">
-        <v>90</v>
+        <v>87.1</v>
       </c>
       <c r="E67">
-        <v>89.4</v>
+        <v>88.2</v>
       </c>
       <c r="F67" t="s">
         <v>47</v>
       </c>
       <c r="H67">
-        <v>32</v>
+        <v>-7</v>
       </c>
       <c r="I67">
-        <v>-66</v>
+        <v>-105</v>
       </c>
       <c r="J67">
         <v>-2</v>
       </c>
       <c r="K67">
-        <v>34</v>
+        <v>-5</v>
       </c>
       <c r="N67">
         <v>100</v>
@@ -1966,7 +1966,7 @@
     </row>
     <row r="68" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C68">
-        <v>0.6</v>
+        <v>-1.1</v>
       </c>
       <c r="E68">
         <f>E64+C68</f>
@@ -1977,22 +1977,22 @@
         <v>15</v>
       </c>
       <c r="C69" s="1">
-        <v>2636</v>
+        <v>2664</v>
       </c>
       <c r="E69" s="1">
-        <v>2572</v>
+        <v>2655</v>
       </c>
       <c r="F69" t="s">
         <v>43</v>
       </c>
       <c r="H69" s="1">
-        <v>2238</v>
+        <v>2254</v>
       </c>
       <c r="I69" s="1">
-        <v>6812</v>
+        <v>6829</v>
       </c>
       <c r="J69">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L69" t="s">
         <v>44</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="70" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C70" s="1">
-        <v>1836</v>
+        <v>1839</v>
       </c>
       <c r="E70" s="1">
-        <v>1765</v>
+        <v>1854</v>
       </c>
       <c r="F70" t="s">
         <v>45</v>
       </c>
       <c r="H70" s="1">
-        <v>2171</v>
+        <v>2257</v>
       </c>
       <c r="I70" s="1">
-        <v>6647</v>
+        <v>6734</v>
       </c>
       <c r="J70">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="L70" t="s">
         <v>46</v>
@@ -2029,25 +2029,25 @@
     </row>
     <row r="71" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C71">
-        <v>80</v>
+        <v>82.5</v>
       </c>
       <c r="E71">
-        <v>80.7</v>
+        <v>80.1</v>
       </c>
       <c r="F71" t="s">
         <v>47</v>
       </c>
       <c r="H71">
-        <v>67</v>
+        <v>-3</v>
       </c>
       <c r="I71">
-        <v>165</v>
+        <v>95</v>
       </c>
       <c r="J71">
         <v>2</v>
       </c>
       <c r="K71">
-        <v>65</v>
+        <v>-5</v>
       </c>
       <c r="N71">
         <v>100</v>
@@ -2055,7 +2055,7 @@
     </row>
     <row r="72" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C72">
-        <v>-0.7</v>
+        <v>2.4</v>
       </c>
       <c r="E72">
         <f>E68+C72</f>
@@ -2066,19 +2066,19 @@
         <v>16</v>
       </c>
       <c r="C73" s="1">
-        <v>2625</v>
+        <v>2700</v>
       </c>
       <c r="E73" s="1">
-        <v>2632</v>
+        <v>2705</v>
       </c>
       <c r="F73" t="s">
         <v>43</v>
       </c>
       <c r="H73" s="1">
-        <v>2176</v>
+        <v>2265</v>
       </c>
       <c r="I73" s="1">
-        <v>6651</v>
+        <v>6740</v>
       </c>
       <c r="J73">
         <v>0</v>
@@ -2092,19 +2092,19 @@
     </row>
     <row r="74" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C74" s="1">
-        <v>1725</v>
+        <v>1828</v>
       </c>
       <c r="E74" s="1">
-        <v>1739</v>
+        <v>1840</v>
       </c>
       <c r="F74" t="s">
         <v>45</v>
       </c>
       <c r="H74" s="1">
-        <v>2187</v>
+        <v>2273</v>
       </c>
       <c r="I74" s="1">
-        <v>6760</v>
+        <v>6846</v>
       </c>
       <c r="J74">
         <v>2</v>
@@ -2118,25 +2118,25 @@
     </row>
     <row r="75" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C75">
-        <v>90</v>
+        <v>87.2</v>
       </c>
       <c r="E75">
-        <v>89.3</v>
+        <v>86.5</v>
       </c>
       <c r="F75" t="s">
         <v>47</v>
       </c>
       <c r="H75">
-        <v>-11</v>
+        <v>-8</v>
       </c>
       <c r="I75">
-        <v>-109</v>
+        <v>-106</v>
       </c>
       <c r="J75">
         <v>-2</v>
       </c>
       <c r="K75">
-        <v>-9</v>
+        <v>-6</v>
       </c>
       <c r="N75">
         <v>100</v>
@@ -2155,22 +2155,22 @@
         <v>17</v>
       </c>
       <c r="C77" s="1">
-        <v>2640</v>
+        <v>2719</v>
       </c>
       <c r="E77" s="1">
-        <v>2597</v>
+        <v>2726</v>
       </c>
       <c r="F77" t="s">
         <v>43</v>
       </c>
       <c r="H77" s="1">
-        <v>2237</v>
+        <v>2288</v>
       </c>
       <c r="I77" s="1">
-        <v>6811</v>
+        <v>6861</v>
       </c>
       <c r="J77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L77" t="s">
         <v>44</v>
@@ -2181,22 +2181,22 @@
     </row>
     <row r="78" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C78" s="1">
-        <v>1834</v>
+        <v>1856</v>
       </c>
       <c r="E78" s="1">
-        <v>1804</v>
+        <v>1862</v>
       </c>
       <c r="F78" t="s">
         <v>45</v>
       </c>
       <c r="H78" s="1">
-        <v>2200</v>
+        <v>2294</v>
       </c>
       <c r="I78" s="1">
-        <v>6676</v>
+        <v>6769</v>
       </c>
       <c r="J78">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L78" t="s">
         <v>46</v>
@@ -2207,25 +2207,25 @@
     </row>
     <row r="79" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C79">
-        <v>80.6</v>
+        <v>86.3</v>
       </c>
       <c r="E79">
-        <v>79.3</v>
+        <v>86.4</v>
       </c>
       <c r="F79" t="s">
         <v>47</v>
       </c>
       <c r="H79">
-        <v>37</v>
+        <v>-6</v>
       </c>
       <c r="I79">
-        <v>135</v>
+        <v>92</v>
       </c>
       <c r="J79">
         <v>2</v>
       </c>
       <c r="K79">
-        <v>35</v>
+        <v>-8</v>
       </c>
       <c r="N79">
         <v>100</v>
@@ -2233,7 +2233,7 @@
     </row>
     <row r="80" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C80">
-        <v>1.3</v>
+        <v>-0.1</v>
       </c>
       <c r="E80">
         <f>E76+C80</f>
@@ -2244,22 +2244,22 @@
         <v>18</v>
       </c>
       <c r="C81" s="1">
-        <v>2653</v>
+        <v>2741</v>
       </c>
       <c r="E81" s="1">
-        <v>2645</v>
+        <v>2750</v>
       </c>
       <c r="F81" t="s">
         <v>43</v>
       </c>
       <c r="H81" s="1">
-        <v>2205</v>
+        <v>2305</v>
       </c>
       <c r="I81" s="1">
-        <v>6681</v>
+        <v>6782</v>
       </c>
       <c r="J81">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="L81" t="s">
         <v>46</v>
@@ -2270,22 +2270,22 @@
     </row>
     <row r="82" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C82" s="1">
-        <v>1753</v>
+        <v>1865</v>
       </c>
       <c r="E82" s="1">
-        <v>1773</v>
+        <v>1864</v>
       </c>
       <c r="F82" t="s">
         <v>45</v>
       </c>
       <c r="H82" s="1">
-        <v>2210</v>
+        <v>2309</v>
       </c>
       <c r="I82" s="1">
-        <v>6784</v>
+        <v>6884</v>
       </c>
       <c r="J82">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L82" t="s">
         <v>44</v>
@@ -2296,25 +2296,25 @@
     </row>
     <row r="83" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C83">
-        <v>90</v>
+        <v>87.6</v>
       </c>
       <c r="E83">
-        <v>87.2</v>
+        <v>88.6</v>
       </c>
       <c r="F83" t="s">
         <v>47</v>
       </c>
       <c r="H83">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="I83">
-        <v>-103</v>
+        <v>-102</v>
       </c>
       <c r="J83">
         <v>-2</v>
       </c>
       <c r="K83">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="N83">
         <v>100</v>
@@ -2322,7 +2322,7 @@
     </row>
     <row r="84" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C84">
-        <v>2.8</v>
+        <v>-1</v>
       </c>
       <c r="E84">
         <f>E80+C84</f>
@@ -2333,22 +2333,22 @@
         <v>19</v>
       </c>
       <c r="C85" s="1">
-        <v>2680</v>
+        <v>2740</v>
       </c>
       <c r="E85" s="1">
-        <v>2607</v>
+        <v>2734</v>
       </c>
       <c r="F85" t="s">
         <v>43</v>
       </c>
       <c r="H85" s="1">
-        <v>2282</v>
+        <v>2316</v>
       </c>
       <c r="I85" s="1">
-        <v>6857</v>
+        <v>6890</v>
       </c>
       <c r="J85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L85" t="s">
         <v>44</v>
@@ -2359,22 +2359,22 @@
     </row>
     <row r="86" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C86" s="1">
-        <v>1880</v>
+        <v>1896</v>
       </c>
       <c r="E86" s="1">
-        <v>1847</v>
+        <v>1908</v>
       </c>
       <c r="F86" t="s">
         <v>45</v>
       </c>
       <c r="H86" s="1">
-        <v>2230</v>
+        <v>2320</v>
       </c>
       <c r="I86" s="1">
-        <v>6707</v>
+        <v>6796</v>
       </c>
       <c r="J86">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L86" t="s">
         <v>46</v>
@@ -2385,25 +2385,25 @@
     </row>
     <row r="87" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C87">
-        <v>80</v>
+        <v>84.4</v>
       </c>
       <c r="E87">
-        <v>76</v>
+        <v>82.6</v>
       </c>
       <c r="F87" t="s">
         <v>47</v>
       </c>
       <c r="H87">
-        <v>52</v>
+        <v>-4</v>
       </c>
       <c r="I87">
-        <v>150</v>
+        <v>94</v>
       </c>
       <c r="J87">
         <v>2</v>
       </c>
       <c r="K87">
-        <v>50</v>
+        <v>-6</v>
       </c>
       <c r="N87">
         <v>100</v>
@@ -2411,7 +2411,7 @@
     </row>
     <row r="88" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C88">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="E88">
         <f>E84+C88</f>
@@ -2422,19 +2422,19 @@
         <v>20</v>
       </c>
       <c r="C89" s="1">
-        <v>2717</v>
+        <v>2751</v>
       </c>
       <c r="E89" s="1">
-        <v>2669</v>
+        <v>2762</v>
       </c>
       <c r="F89" t="s">
         <v>43</v>
       </c>
       <c r="H89" s="1">
-        <v>2265</v>
+        <v>2329</v>
       </c>
       <c r="I89" s="1">
-        <v>6741</v>
+        <v>6805</v>
       </c>
       <c r="J89">
         <v>-1</v>
@@ -2448,19 +2448,19 @@
     </row>
     <row r="90" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C90" s="1">
-        <v>1817</v>
+        <v>1904</v>
       </c>
       <c r="E90" s="1">
-        <v>1812</v>
+        <v>1908</v>
       </c>
       <c r="F90" t="s">
         <v>45</v>
       </c>
       <c r="H90" s="1">
-        <v>2240</v>
+        <v>2335</v>
       </c>
       <c r="I90" s="1">
-        <v>6814</v>
+        <v>6909</v>
       </c>
       <c r="J90">
         <v>1</v>
@@ -2474,25 +2474,25 @@
     </row>
     <row r="91" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C91">
-        <v>90</v>
+        <v>84.7</v>
       </c>
       <c r="E91">
-        <v>85.7</v>
+        <v>85.4</v>
       </c>
       <c r="F91" t="s">
         <v>47</v>
       </c>
       <c r="H91">
-        <v>25</v>
+        <v>-6</v>
       </c>
       <c r="I91">
-        <v>-73</v>
+        <v>-104</v>
       </c>
       <c r="J91">
         <v>-2</v>
       </c>
       <c r="K91">
-        <v>27</v>
+        <v>-4</v>
       </c>
       <c r="N91">
         <v>100</v>
@@ -2500,7 +2500,7 @@
     </row>
     <row r="92" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C92">
-        <v>4.3</v>
+        <v>-0.7</v>
       </c>
       <c r="E92">
         <f>E88+C92</f>
@@ -2511,22 +2511,22 @@
         <v>21</v>
       </c>
       <c r="C93" s="1">
-        <v>2694</v>
+        <v>2779</v>
       </c>
       <c r="E93" s="1">
-        <v>2652</v>
+        <v>2778</v>
       </c>
       <c r="F93" t="s">
         <v>43</v>
       </c>
       <c r="H93" s="1">
-        <v>2296</v>
+        <v>2351</v>
       </c>
       <c r="I93" s="1">
-        <v>6871</v>
+        <v>6925</v>
       </c>
       <c r="J93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L93" t="s">
         <v>44</v>
@@ -2537,22 +2537,22 @@
     </row>
     <row r="94" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C94" s="1">
-        <v>1894</v>
+        <v>1920</v>
       </c>
       <c r="E94" s="1">
-        <v>1879</v>
+        <v>1927</v>
       </c>
       <c r="F94" t="s">
         <v>45</v>
       </c>
       <c r="H94" s="1">
-        <v>2263</v>
+        <v>2357</v>
       </c>
       <c r="I94" s="1">
-        <v>6740</v>
+        <v>6833</v>
       </c>
       <c r="J94">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L94" t="s">
         <v>46</v>
@@ -2563,25 +2563,25 @@
     </row>
     <row r="95" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C95">
-        <v>80</v>
+        <v>85.9</v>
       </c>
       <c r="E95">
-        <v>77.3</v>
+        <v>85.1</v>
       </c>
       <c r="F95" t="s">
         <v>47</v>
       </c>
       <c r="H95">
-        <v>33</v>
+        <v>-6</v>
       </c>
       <c r="I95">
-        <v>131</v>
+        <v>92</v>
       </c>
       <c r="J95">
         <v>2</v>
       </c>
       <c r="K95">
-        <v>31</v>
+        <v>-8</v>
       </c>
       <c r="N95">
         <v>100</v>
@@ -2589,7 +2589,7 @@
     </row>
     <row r="96" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C96">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
       <c r="E96">
         <f>E92+C96</f>
@@ -2600,42 +2600,42 @@
         <v>48</v>
       </c>
       <c r="C97">
-        <v>53760</v>
+        <v>55469</v>
       </c>
       <c r="E97">
-        <v>53243</v>
+        <v>54949</v>
       </c>
       <c r="F97" t="s">
         <v>43</v>
       </c>
       <c r="H97">
-        <v>44795</v>
+        <v>46501</v>
       </c>
       <c r="I97">
-        <v>139870</v>
+        <v>141584</v>
       </c>
       <c r="J97">
-        <v>0</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="98" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C98">
-        <v>35811</v>
+        <v>37520</v>
       </c>
       <c r="E98">
-        <v>35262</v>
+        <v>36968</v>
       </c>
       <c r="F98" t="s">
         <v>45</v>
       </c>
       <c r="H98">
-        <v>44258</v>
+        <v>45964</v>
       </c>
       <c r="I98">
-        <v>139232</v>
+        <v>140946</v>
       </c>
       <c r="J98">
-        <v>1</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="99" spans="3:11" x14ac:dyDescent="0.25">
